--- a/artfynd/A 55030-2024 artfynd.xlsx
+++ b/artfynd/A 55030-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122507150</v>
+        <v>122507142</v>
       </c>
       <c r="B2" t="n">
         <v>57379</v>
@@ -693,11 +693,6 @@
       <c r="E2" t="n">
         <v>100109</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509389</v>
+        <v>509307</v>
       </c>
       <c r="R2" t="n">
-        <v>7107890</v>
+        <v>7107977</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122507141</v>
+        <v>122507153</v>
       </c>
       <c r="B3" t="n">
         <v>57379</v>
@@ -800,11 +795,6 @@
       <c r="E3" t="n">
         <v>100109</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -822,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509290</v>
+        <v>509398</v>
       </c>
       <c r="R3" t="n">
-        <v>7107974</v>
+        <v>7107862</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122507161</v>
+        <v>122507152</v>
       </c>
       <c r="B4" t="n">
         <v>57379</v>
@@ -907,11 +897,6 @@
       <c r="E4" t="n">
         <v>100109</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -929,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509403</v>
+        <v>509408</v>
       </c>
       <c r="R4" t="n">
-        <v>7107783</v>
+        <v>7107858</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +954,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122507135</v>
+        <v>122507140</v>
       </c>
       <c r="B5" t="n">
         <v>57379</v>
@@ -1014,11 +999,6 @@
       <c r="E5" t="n">
         <v>100109</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1036,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509339</v>
+        <v>509279</v>
       </c>
       <c r="R5" t="n">
-        <v>7107799</v>
+        <v>7107952</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122507143</v>
+        <v>122507149</v>
       </c>
       <c r="B6" t="n">
         <v>57379</v>
@@ -1121,11 +1101,6 @@
       <c r="E6" t="n">
         <v>100109</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1143,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509335</v>
+        <v>509392</v>
       </c>
       <c r="R6" t="n">
-        <v>7107936</v>
+        <v>7107885</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122507169</v>
+        <v>122507137</v>
       </c>
       <c r="B7" t="n">
-        <v>57532</v>
+        <v>57379</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,38 +1201,29 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Myrsnipmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>509389</v>
+        <v>509318</v>
       </c>
       <c r="R7" t="n">
-        <v>7107816</v>
+        <v>7107804</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,6 +1256,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122507146</v>
+        <v>122507134</v>
       </c>
       <c r="B8" t="n">
         <v>57379</v>
@@ -1334,11 +1305,6 @@
       <c r="E8" t="n">
         <v>100109</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1356,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>509321</v>
+        <v>509339</v>
       </c>
       <c r="R8" t="n">
-        <v>7107910</v>
+        <v>7107807</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1396,7 +1362,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1423,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122507154</v>
+        <v>122507145</v>
       </c>
       <c r="B9" t="n">
         <v>57379</v>
@@ -1441,11 +1407,6 @@
       <c r="E9" t="n">
         <v>100109</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1463,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509380</v>
+        <v>509335</v>
       </c>
       <c r="R9" t="n">
-        <v>7107864</v>
+        <v>7107908</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1530,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122507142</v>
+        <v>122507169</v>
       </c>
       <c r="B10" t="n">
-        <v>57379</v>
+        <v>57532</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1546,34 +1507,33 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>103021</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Myrsnipmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509307</v>
+        <v>509389</v>
       </c>
       <c r="R10" t="n">
-        <v>7107977</v>
+        <v>7107816</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,11 +1566,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1637,7 +1592,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122507136</v>
+        <v>122507165</v>
       </c>
       <c r="B11" t="n">
         <v>57379</v>
@@ -1655,11 +1610,6 @@
       <c r="E11" t="n">
         <v>100109</v>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1677,10 +1627,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509333</v>
+        <v>509420</v>
       </c>
       <c r="R11" t="n">
-        <v>7107799</v>
+        <v>7107746</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1744,7 +1694,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122507147</v>
+        <v>122507144</v>
       </c>
       <c r="B12" t="n">
         <v>57379</v>
@@ -1762,11 +1712,6 @@
       <c r="E12" t="n">
         <v>100109</v>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1784,10 +1729,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>509307</v>
+        <v>509334</v>
       </c>
       <c r="R12" t="n">
-        <v>7107890</v>
+        <v>7107923</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1824,7 +1769,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1851,7 +1796,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122507158</v>
+        <v>122507161</v>
       </c>
       <c r="B13" t="n">
         <v>57379</v>
@@ -1869,11 +1814,6 @@
       <c r="E13" t="n">
         <v>100109</v>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1891,10 +1831,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>509396</v>
+        <v>509403</v>
       </c>
       <c r="R13" t="n">
-        <v>7107815</v>
+        <v>7107783</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1931,7 +1871,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1958,7 +1898,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122507148</v>
+        <v>122507143</v>
       </c>
       <c r="B14" t="n">
         <v>57379</v>
@@ -1976,11 +1916,6 @@
       <c r="E14" t="n">
         <v>100109</v>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1998,10 +1933,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>509350</v>
+        <v>509335</v>
       </c>
       <c r="R14" t="n">
-        <v>7107857</v>
+        <v>7107936</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2038,7 +1973,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2065,7 +2000,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122507153</v>
+        <v>122507154</v>
       </c>
       <c r="B15" t="n">
         <v>57379</v>
@@ -2083,11 +2018,6 @@
       <c r="E15" t="n">
         <v>100109</v>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2105,10 +2035,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>509398</v>
+        <v>509380</v>
       </c>
       <c r="R15" t="n">
-        <v>7107862</v>
+        <v>7107864</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2145,7 +2075,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2172,10 +2102,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122507167</v>
+        <v>122507173</v>
       </c>
       <c r="B16" t="n">
-        <v>57379</v>
+        <v>90831</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2188,21 +2118,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>5432</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2212,10 +2137,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>509416</v>
+        <v>509355</v>
       </c>
       <c r="R16" t="n">
-        <v>7107735</v>
+        <v>7107795</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2248,11 +2173,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2279,7 +2199,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122507159</v>
+        <v>122507138</v>
       </c>
       <c r="B17" t="n">
         <v>57379</v>
@@ -2297,11 +2217,6 @@
       <c r="E17" t="n">
         <v>100109</v>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2319,10 +2234,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>509402</v>
+        <v>509236</v>
       </c>
       <c r="R17" t="n">
-        <v>7107791</v>
+        <v>7107905</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2359,7 +2274,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2386,10 +2301,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122507138</v>
+        <v>122507175</v>
       </c>
       <c r="B18" t="n">
-        <v>57379</v>
+        <v>90831</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2402,21 +2317,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>5432</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2426,10 +2336,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>509236</v>
+        <v>509283</v>
       </c>
       <c r="R18" t="n">
-        <v>7107905</v>
+        <v>7107892</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2462,11 +2372,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2493,7 +2398,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122507145</v>
+        <v>122507146</v>
       </c>
       <c r="B19" t="n">
         <v>57379</v>
@@ -2511,11 +2416,6 @@
       <c r="E19" t="n">
         <v>100109</v>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2533,10 +2433,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>509335</v>
+        <v>509321</v>
       </c>
       <c r="R19" t="n">
-        <v>7107908</v>
+        <v>7107910</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2573,7 +2473,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2600,7 +2500,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122507155</v>
+        <v>122507163</v>
       </c>
       <c r="B20" t="n">
         <v>57379</v>
@@ -2618,11 +2518,6 @@
       <c r="E20" t="n">
         <v>100109</v>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2640,10 +2535,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>509385</v>
+        <v>509410</v>
       </c>
       <c r="R20" t="n">
-        <v>7107815</v>
+        <v>7107764</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2680,7 +2575,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2707,7 +2602,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122507163</v>
+        <v>122507136</v>
       </c>
       <c r="B21" t="n">
         <v>57379</v>
@@ -2725,11 +2620,6 @@
       <c r="E21" t="n">
         <v>100109</v>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2747,10 +2637,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>509410</v>
+        <v>509333</v>
       </c>
       <c r="R21" t="n">
-        <v>7107764</v>
+        <v>7107799</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2814,10 +2704,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122507175</v>
+        <v>122507147</v>
       </c>
       <c r="B22" t="n">
-        <v>90826</v>
+        <v>57379</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2830,21 +2720,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2854,10 +2739,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>509283</v>
+        <v>509307</v>
       </c>
       <c r="R22" t="n">
-        <v>7107892</v>
+        <v>7107890</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2890,6 +2775,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2916,7 +2806,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122507140</v>
+        <v>122507150</v>
       </c>
       <c r="B23" t="n">
         <v>57379</v>
@@ -2934,11 +2824,6 @@
       <c r="E23" t="n">
         <v>100109</v>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2956,10 +2841,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>509279</v>
+        <v>509389</v>
       </c>
       <c r="R23" t="n">
-        <v>7107952</v>
+        <v>7107890</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3023,10 +2908,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122507173</v>
+        <v>122507148</v>
       </c>
       <c r="B24" t="n">
-        <v>90826</v>
+        <v>57379</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3039,21 +2924,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3063,10 +2943,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>509355</v>
+        <v>509350</v>
       </c>
       <c r="R24" t="n">
-        <v>7107795</v>
+        <v>7107857</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3099,6 +2979,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3125,7 +3010,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122507152</v>
+        <v>122507159</v>
       </c>
       <c r="B25" t="n">
         <v>57379</v>
@@ -3143,11 +3028,6 @@
       <c r="E25" t="n">
         <v>100109</v>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -3165,10 +3045,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>509408</v>
+        <v>509402</v>
       </c>
       <c r="R25" t="n">
-        <v>7107858</v>
+        <v>7107791</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3205,7 +3085,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3232,7 +3112,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122507165</v>
+        <v>122507141</v>
       </c>
       <c r="B26" t="n">
         <v>57379</v>
@@ -3250,11 +3130,6 @@
       <c r="E26" t="n">
         <v>100109</v>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -3272,10 +3147,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>509420</v>
+        <v>509290</v>
       </c>
       <c r="R26" t="n">
-        <v>7107746</v>
+        <v>7107974</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3342,7 +3217,7 @@
         <v>122507170</v>
       </c>
       <c r="B27" t="n">
-        <v>79732</v>
+        <v>79733</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3356,11 +3231,6 @@
       </c>
       <c r="E27" t="n">
         <v>6458</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -3441,7 +3311,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122507149</v>
+        <v>122507167</v>
       </c>
       <c r="B28" t="n">
         <v>57379</v>
@@ -3459,11 +3329,6 @@
       <c r="E28" t="n">
         <v>100109</v>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G28" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -3481,10 +3346,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>509392</v>
+        <v>509416</v>
       </c>
       <c r="R28" t="n">
-        <v>7107885</v>
+        <v>7107735</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3521,7 +3386,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3548,7 +3413,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122507151</v>
+        <v>122507158</v>
       </c>
       <c r="B29" t="n">
         <v>57379</v>
@@ -3566,11 +3431,6 @@
       <c r="E29" t="n">
         <v>100109</v>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G29" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -3588,10 +3448,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>509412</v>
+        <v>509396</v>
       </c>
       <c r="R29" t="n">
-        <v>7107874</v>
+        <v>7107815</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3628,7 +3488,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3655,7 +3515,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122507134</v>
+        <v>122507155</v>
       </c>
       <c r="B30" t="n">
         <v>57379</v>
@@ -3673,11 +3533,6 @@
       <c r="E30" t="n">
         <v>100109</v>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G30" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -3695,10 +3550,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>509339</v>
+        <v>509385</v>
       </c>
       <c r="R30" t="n">
-        <v>7107807</v>
+        <v>7107815</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3735,7 +3590,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3762,7 +3617,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122507144</v>
+        <v>122507135</v>
       </c>
       <c r="B31" t="n">
         <v>57379</v>
@@ -3780,11 +3635,6 @@
       <c r="E31" t="n">
         <v>100109</v>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G31" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -3802,10 +3652,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>509334</v>
+        <v>509339</v>
       </c>
       <c r="R31" t="n">
-        <v>7107923</v>
+        <v>7107799</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3842,7 +3692,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3869,7 +3719,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122507137</v>
+        <v>122507151</v>
       </c>
       <c r="B32" t="n">
         <v>57379</v>
@@ -3887,11 +3737,6 @@
       <c r="E32" t="n">
         <v>100109</v>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -3909,10 +3754,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>509318</v>
+        <v>509412</v>
       </c>
       <c r="R32" t="n">
-        <v>7107804</v>
+        <v>7107874</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3949,7 +3794,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 55030-2024 artfynd.xlsx
+++ b/artfynd/A 55030-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122507142</v>
+        <v>122507150</v>
       </c>
       <c r="B2" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -693,6 +693,11 @@
       <c r="E2" t="n">
         <v>100109</v>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -710,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509307</v>
+        <v>509389</v>
       </c>
       <c r="R2" t="n">
-        <v>7107977</v>
+        <v>7107890</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122507153</v>
+        <v>122507136</v>
       </c>
       <c r="B3" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -795,6 +800,11 @@
       <c r="E3" t="n">
         <v>100109</v>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -812,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509398</v>
+        <v>509333</v>
       </c>
       <c r="R3" t="n">
-        <v>7107862</v>
+        <v>7107799</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122507152</v>
+        <v>122507149</v>
       </c>
       <c r="B4" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -897,6 +907,11 @@
       <c r="E4" t="n">
         <v>100109</v>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -914,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509408</v>
+        <v>509392</v>
       </c>
       <c r="R4" t="n">
-        <v>7107858</v>
+        <v>7107885</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122507140</v>
+        <v>122507145</v>
       </c>
       <c r="B5" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -999,6 +1014,11 @@
       <c r="E5" t="n">
         <v>100109</v>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1016,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509279</v>
+        <v>509335</v>
       </c>
       <c r="R5" t="n">
-        <v>7107952</v>
+        <v>7107908</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122507149</v>
+        <v>122507173</v>
       </c>
       <c r="B6" t="n">
-        <v>57379</v>
+        <v>90844</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,16 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1118,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509392</v>
+        <v>509355</v>
       </c>
       <c r="R6" t="n">
-        <v>7107885</v>
+        <v>7107795</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1154,11 +1179,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122507137</v>
+        <v>122507152</v>
       </c>
       <c r="B7" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1203,6 +1223,11 @@
       <c r="E7" t="n">
         <v>100109</v>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1220,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>509318</v>
+        <v>509408</v>
       </c>
       <c r="R7" t="n">
-        <v>7107804</v>
+        <v>7107858</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122507134</v>
+        <v>122507141</v>
       </c>
       <c r="B8" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1305,6 +1330,11 @@
       <c r="E8" t="n">
         <v>100109</v>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1322,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>509339</v>
+        <v>509290</v>
       </c>
       <c r="R8" t="n">
-        <v>7107807</v>
+        <v>7107974</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122507145</v>
+        <v>122507169</v>
       </c>
       <c r="B9" t="n">
-        <v>57379</v>
+        <v>57536</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,29 +1435,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>103021</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Myrsnipmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509335</v>
+        <v>509389</v>
       </c>
       <c r="R9" t="n">
-        <v>7107908</v>
+        <v>7107816</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1460,11 +1499,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1491,10 +1525,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122507169</v>
+        <v>122507135</v>
       </c>
       <c r="B10" t="n">
-        <v>57532</v>
+        <v>57383</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,33 +1541,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Myrsnipmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509389</v>
+        <v>509339</v>
       </c>
       <c r="R10" t="n">
-        <v>7107816</v>
+        <v>7107799</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,6 +1601,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1592,10 +1632,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122507165</v>
+        <v>122507146</v>
       </c>
       <c r="B11" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,6 +1650,11 @@
       <c r="E11" t="n">
         <v>100109</v>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1627,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509420</v>
+        <v>509321</v>
       </c>
       <c r="R11" t="n">
-        <v>7107746</v>
+        <v>7107910</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1667,7 +1712,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1694,10 +1739,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122507144</v>
+        <v>122507158</v>
       </c>
       <c r="B12" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1712,6 +1757,11 @@
       <c r="E12" t="n">
         <v>100109</v>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1729,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>509334</v>
+        <v>509396</v>
       </c>
       <c r="R12" t="n">
-        <v>7107923</v>
+        <v>7107815</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1769,7 +1819,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1796,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122507161</v>
+        <v>122507165</v>
       </c>
       <c r="B13" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1814,6 +1864,11 @@
       <c r="E13" t="n">
         <v>100109</v>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1831,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>509403</v>
+        <v>509420</v>
       </c>
       <c r="R13" t="n">
-        <v>7107783</v>
+        <v>7107746</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1898,10 +1953,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122507143</v>
+        <v>122507153</v>
       </c>
       <c r="B14" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1916,6 +1971,11 @@
       <c r="E14" t="n">
         <v>100109</v>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1933,10 +1993,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>509335</v>
+        <v>509398</v>
       </c>
       <c r="R14" t="n">
-        <v>7107936</v>
+        <v>7107862</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1973,7 +2033,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2000,10 +2060,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122507154</v>
+        <v>122507140</v>
       </c>
       <c r="B15" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2018,6 +2078,11 @@
       <c r="E15" t="n">
         <v>100109</v>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2035,10 +2100,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>509380</v>
+        <v>509279</v>
       </c>
       <c r="R15" t="n">
-        <v>7107864</v>
+        <v>7107952</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2075,7 +2140,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2102,10 +2167,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122507173</v>
+        <v>122507163</v>
       </c>
       <c r="B16" t="n">
-        <v>90831</v>
+        <v>57383</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2118,16 +2183,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2137,10 +2207,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>509355</v>
+        <v>509410</v>
       </c>
       <c r="R16" t="n">
-        <v>7107795</v>
+        <v>7107764</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2173,6 +2243,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2199,10 +2274,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122507138</v>
+        <v>122507142</v>
       </c>
       <c r="B17" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,6 +2292,11 @@
       <c r="E17" t="n">
         <v>100109</v>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2234,10 +2314,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>509236</v>
+        <v>509307</v>
       </c>
       <c r="R17" t="n">
-        <v>7107905</v>
+        <v>7107977</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2274,7 +2354,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2301,10 +2381,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122507175</v>
+        <v>122507159</v>
       </c>
       <c r="B18" t="n">
-        <v>90831</v>
+        <v>57383</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2317,16 +2397,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2336,10 +2421,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>509283</v>
+        <v>509402</v>
       </c>
       <c r="R18" t="n">
-        <v>7107892</v>
+        <v>7107791</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2372,6 +2457,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2398,10 +2488,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122507146</v>
+        <v>122507155</v>
       </c>
       <c r="B19" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2416,6 +2506,11 @@
       <c r="E19" t="n">
         <v>100109</v>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2433,10 +2528,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>509321</v>
+        <v>509385</v>
       </c>
       <c r="R19" t="n">
-        <v>7107910</v>
+        <v>7107815</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2500,10 +2595,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122507163</v>
+        <v>122507151</v>
       </c>
       <c r="B20" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2518,6 +2613,11 @@
       <c r="E20" t="n">
         <v>100109</v>
       </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2535,10 +2635,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>509410</v>
+        <v>509412</v>
       </c>
       <c r="R20" t="n">
-        <v>7107764</v>
+        <v>7107874</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2575,7 +2675,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2602,10 +2702,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122507136</v>
+        <v>122507154</v>
       </c>
       <c r="B21" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2620,6 +2720,11 @@
       <c r="E21" t="n">
         <v>100109</v>
       </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2637,10 +2742,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>509333</v>
+        <v>509380</v>
       </c>
       <c r="R21" t="n">
-        <v>7107799</v>
+        <v>7107864</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2704,10 +2809,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122507147</v>
+        <v>122507137</v>
       </c>
       <c r="B22" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2722,6 +2827,11 @@
       <c r="E22" t="n">
         <v>100109</v>
       </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2739,10 +2849,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>509307</v>
+        <v>509318</v>
       </c>
       <c r="R22" t="n">
-        <v>7107890</v>
+        <v>7107804</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2806,10 +2916,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122507150</v>
+        <v>122507167</v>
       </c>
       <c r="B23" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2824,6 +2934,11 @@
       <c r="E23" t="n">
         <v>100109</v>
       </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2841,10 +2956,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>509389</v>
+        <v>509416</v>
       </c>
       <c r="R23" t="n">
-        <v>7107890</v>
+        <v>7107735</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2908,10 +3023,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122507148</v>
+        <v>122507138</v>
       </c>
       <c r="B24" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2926,6 +3041,11 @@
       <c r="E24" t="n">
         <v>100109</v>
       </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -2943,10 +3063,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>509350</v>
+        <v>509236</v>
       </c>
       <c r="R24" t="n">
-        <v>7107857</v>
+        <v>7107905</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2983,7 +3103,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3010,10 +3130,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122507159</v>
+        <v>122507134</v>
       </c>
       <c r="B25" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3028,6 +3148,11 @@
       <c r="E25" t="n">
         <v>100109</v>
       </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -3045,10 +3170,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>509402</v>
+        <v>509339</v>
       </c>
       <c r="R25" t="n">
-        <v>7107791</v>
+        <v>7107807</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3112,10 +3237,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122507141</v>
+        <v>122507147</v>
       </c>
       <c r="B26" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3130,6 +3255,11 @@
       <c r="E26" t="n">
         <v>100109</v>
       </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -3147,10 +3277,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>509290</v>
+        <v>509307</v>
       </c>
       <c r="R26" t="n">
-        <v>7107974</v>
+        <v>7107890</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3187,7 +3317,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3214,10 +3344,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122507170</v>
+        <v>122507143</v>
       </c>
       <c r="B27" t="n">
-        <v>79733</v>
+        <v>57383</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3230,16 +3360,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3249,10 +3384,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>509393</v>
+        <v>509335</v>
       </c>
       <c r="R27" t="n">
-        <v>7107823</v>
+        <v>7107936</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3285,6 +3420,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3311,10 +3451,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122507167</v>
+        <v>122507144</v>
       </c>
       <c r="B28" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3329,6 +3469,11 @@
       <c r="E28" t="n">
         <v>100109</v>
       </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -3346,10 +3491,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>509416</v>
+        <v>509334</v>
       </c>
       <c r="R28" t="n">
-        <v>7107735</v>
+        <v>7107923</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3386,7 +3531,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3413,10 +3558,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122507158</v>
+        <v>122507148</v>
       </c>
       <c r="B29" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3431,6 +3576,11 @@
       <c r="E29" t="n">
         <v>100109</v>
       </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -3448,10 +3598,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>509396</v>
+        <v>509350</v>
       </c>
       <c r="R29" t="n">
-        <v>7107815</v>
+        <v>7107857</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3488,7 +3638,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3515,10 +3665,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122507155</v>
+        <v>122507161</v>
       </c>
       <c r="B30" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3533,6 +3683,11 @@
       <c r="E30" t="n">
         <v>100109</v>
       </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -3550,10 +3705,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>509385</v>
+        <v>509403</v>
       </c>
       <c r="R30" t="n">
-        <v>7107815</v>
+        <v>7107783</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3590,7 +3745,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3617,10 +3772,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122507135</v>
+        <v>122507170</v>
       </c>
       <c r="B31" t="n">
-        <v>57379</v>
+        <v>79737</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3633,16 +3788,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6458</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3652,10 +3812,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>509339</v>
+        <v>509393</v>
       </c>
       <c r="R31" t="n">
-        <v>7107799</v>
+        <v>7107823</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3688,11 +3848,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3719,10 +3874,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122507151</v>
+        <v>122507175</v>
       </c>
       <c r="B32" t="n">
-        <v>57379</v>
+        <v>90844</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3735,16 +3890,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5432</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3754,10 +3914,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>509412</v>
+        <v>509283</v>
       </c>
       <c r="R32" t="n">
-        <v>7107874</v>
+        <v>7107892</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3790,11 +3950,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 55030-2024 artfynd.xlsx
+++ b/artfynd/A 55030-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122507150</v>
+        <v>122507149</v>
       </c>
       <c r="B2" t="n">
         <v>57383</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509389</v>
+        <v>509392</v>
       </c>
       <c r="R2" t="n">
-        <v>7107890</v>
+        <v>7107885</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122507136</v>
+        <v>122507152</v>
       </c>
       <c r="B3" t="n">
         <v>57383</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509333</v>
+        <v>509408</v>
       </c>
       <c r="R3" t="n">
-        <v>7107799</v>
+        <v>7107858</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122507149</v>
+        <v>122507136</v>
       </c>
       <c r="B4" t="n">
         <v>57383</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509392</v>
+        <v>509333</v>
       </c>
       <c r="R4" t="n">
-        <v>7107885</v>
+        <v>7107799</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122507145</v>
+        <v>122507167</v>
       </c>
       <c r="B5" t="n">
         <v>57383</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509335</v>
+        <v>509416</v>
       </c>
       <c r="R5" t="n">
-        <v>7107908</v>
+        <v>7107735</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122507173</v>
+        <v>122507158</v>
       </c>
       <c r="B6" t="n">
-        <v>90844</v>
+        <v>57383</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509355</v>
+        <v>509396</v>
       </c>
       <c r="R6" t="n">
-        <v>7107795</v>
+        <v>7107815</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,6 +1179,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122507152</v>
+        <v>122507144</v>
       </c>
       <c r="B7" t="n">
         <v>57383</v>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>509408</v>
+        <v>509334</v>
       </c>
       <c r="R7" t="n">
-        <v>7107858</v>
+        <v>7107923</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122507141</v>
+        <v>122507170</v>
       </c>
       <c r="B8" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>509290</v>
+        <v>509393</v>
       </c>
       <c r="R8" t="n">
-        <v>7107974</v>
+        <v>7107823</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,11 +1393,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122507169</v>
+        <v>122507142</v>
       </c>
       <c r="B9" t="n">
-        <v>57536</v>
+        <v>57383</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,38 +1435,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Myrsnipmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509389</v>
+        <v>509307</v>
       </c>
       <c r="R9" t="n">
-        <v>7107816</v>
+        <v>7107977</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,6 +1495,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1525,7 +1526,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122507135</v>
+        <v>122507148</v>
       </c>
       <c r="B10" t="n">
         <v>57383</v>
@@ -1565,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509339</v>
+        <v>509350</v>
       </c>
       <c r="R10" t="n">
-        <v>7107799</v>
+        <v>7107857</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1632,7 +1633,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122507146</v>
+        <v>122507138</v>
       </c>
       <c r="B11" t="n">
         <v>57383</v>
@@ -1672,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509321</v>
+        <v>509236</v>
       </c>
       <c r="R11" t="n">
-        <v>7107910</v>
+        <v>7107905</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1712,7 +1713,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1739,7 +1740,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122507158</v>
+        <v>122507159</v>
       </c>
       <c r="B12" t="n">
         <v>57383</v>
@@ -1779,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>509396</v>
+        <v>509402</v>
       </c>
       <c r="R12" t="n">
-        <v>7107815</v>
+        <v>7107791</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1819,7 +1820,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1846,7 +1847,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122507165</v>
+        <v>122507141</v>
       </c>
       <c r="B13" t="n">
         <v>57383</v>
@@ -1886,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>509420</v>
+        <v>509290</v>
       </c>
       <c r="R13" t="n">
-        <v>7107746</v>
+        <v>7107974</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1953,7 +1954,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122507153</v>
+        <v>122507151</v>
       </c>
       <c r="B14" t="n">
         <v>57383</v>
@@ -1993,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>509398</v>
+        <v>509412</v>
       </c>
       <c r="R14" t="n">
-        <v>7107862</v>
+        <v>7107874</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2060,10 +2061,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122507140</v>
+        <v>122507169</v>
       </c>
       <c r="B15" t="n">
-        <v>57383</v>
+        <v>57536</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2076,34 +2077,38 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Myrsnipmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>509279</v>
+        <v>509389</v>
       </c>
       <c r="R15" t="n">
-        <v>7107952</v>
+        <v>7107816</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,11 +2141,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2167,7 +2167,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122507163</v>
+        <v>122507143</v>
       </c>
       <c r="B16" t="n">
         <v>57383</v>
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>509410</v>
+        <v>509335</v>
       </c>
       <c r="R16" t="n">
-        <v>7107764</v>
+        <v>7107936</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2274,7 +2274,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122507142</v>
+        <v>122507140</v>
       </c>
       <c r="B17" t="n">
         <v>57383</v>
@@ -2314,10 +2314,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>509307</v>
+        <v>509279</v>
       </c>
       <c r="R17" t="n">
-        <v>7107977</v>
+        <v>7107952</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2381,7 +2381,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122507159</v>
+        <v>122507165</v>
       </c>
       <c r="B18" t="n">
         <v>57383</v>
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>509402</v>
+        <v>509420</v>
       </c>
       <c r="R18" t="n">
-        <v>7107791</v>
+        <v>7107746</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2595,7 +2595,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122507151</v>
+        <v>122507146</v>
       </c>
       <c r="B20" t="n">
         <v>57383</v>
@@ -2635,10 +2635,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>509412</v>
+        <v>509321</v>
       </c>
       <c r="R20" t="n">
-        <v>7107874</v>
+        <v>7107910</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2702,7 +2702,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122507154</v>
+        <v>122507150</v>
       </c>
       <c r="B21" t="n">
         <v>57383</v>
@@ -2742,10 +2742,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>509380</v>
+        <v>509389</v>
       </c>
       <c r="R21" t="n">
-        <v>7107864</v>
+        <v>7107890</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2782,7 +2782,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2809,7 +2809,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122507137</v>
+        <v>122507134</v>
       </c>
       <c r="B22" t="n">
         <v>57383</v>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>509318</v>
+        <v>509339</v>
       </c>
       <c r="R22" t="n">
-        <v>7107804</v>
+        <v>7107807</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2916,7 +2916,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122507167</v>
+        <v>122507135</v>
       </c>
       <c r="B23" t="n">
         <v>57383</v>
@@ -2956,10 +2956,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>509416</v>
+        <v>509339</v>
       </c>
       <c r="R23" t="n">
-        <v>7107735</v>
+        <v>7107799</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3023,10 +3023,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122507138</v>
+        <v>122507175</v>
       </c>
       <c r="B24" t="n">
-        <v>57383</v>
+        <v>90857</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3039,21 +3039,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3063,10 +3063,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>509236</v>
+        <v>509283</v>
       </c>
       <c r="R24" t="n">
-        <v>7107905</v>
+        <v>7107892</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3099,11 +3099,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3130,7 +3125,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122507134</v>
+        <v>122507145</v>
       </c>
       <c r="B25" t="n">
         <v>57383</v>
@@ -3170,10 +3165,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>509339</v>
+        <v>509335</v>
       </c>
       <c r="R25" t="n">
-        <v>7107807</v>
+        <v>7107908</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3344,7 +3339,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122507143</v>
+        <v>122507163</v>
       </c>
       <c r="B27" t="n">
         <v>57383</v>
@@ -3384,10 +3379,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>509335</v>
+        <v>509410</v>
       </c>
       <c r="R27" t="n">
-        <v>7107936</v>
+        <v>7107764</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3451,7 +3446,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122507144</v>
+        <v>122507154</v>
       </c>
       <c r="B28" t="n">
         <v>57383</v>
@@ -3491,10 +3486,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>509334</v>
+        <v>509380</v>
       </c>
       <c r="R28" t="n">
-        <v>7107923</v>
+        <v>7107864</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3558,10 +3553,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122507148</v>
+        <v>122507173</v>
       </c>
       <c r="B29" t="n">
-        <v>57383</v>
+        <v>90857</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3574,21 +3569,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3598,10 +3593,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>509350</v>
+        <v>509355</v>
       </c>
       <c r="R29" t="n">
-        <v>7107857</v>
+        <v>7107795</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3634,11 +3629,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3772,10 +3762,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122507170</v>
+        <v>122507137</v>
       </c>
       <c r="B31" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3788,21 +3778,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3812,10 +3802,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>509393</v>
+        <v>509318</v>
       </c>
       <c r="R31" t="n">
-        <v>7107823</v>
+        <v>7107804</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3848,6 +3838,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3874,10 +3869,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122507175</v>
+        <v>122507153</v>
       </c>
       <c r="B32" t="n">
-        <v>90844</v>
+        <v>57383</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3890,21 +3885,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3914,10 +3909,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>509283</v>
+        <v>509398</v>
       </c>
       <c r="R32" t="n">
-        <v>7107892</v>
+        <v>7107862</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3950,6 +3945,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 55030-2024 artfynd.xlsx
+++ b/artfynd/A 55030-2024 artfynd.xlsx
@@ -3446,10 +3446,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122507154</v>
+        <v>122507173</v>
       </c>
       <c r="B28" t="n">
-        <v>57383</v>
+        <v>90857</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3462,21 +3462,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3486,10 +3486,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>509380</v>
+        <v>509355</v>
       </c>
       <c r="R28" t="n">
-        <v>7107864</v>
+        <v>7107795</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3522,11 +3522,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3553,10 +3548,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122507173</v>
+        <v>122507161</v>
       </c>
       <c r="B29" t="n">
-        <v>90857</v>
+        <v>57383</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3569,21 +3564,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3593,10 +3588,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>509355</v>
+        <v>509403</v>
       </c>
       <c r="R29" t="n">
-        <v>7107795</v>
+        <v>7107783</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3629,6 +3624,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3655,7 +3655,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122507161</v>
+        <v>122507154</v>
       </c>
       <c r="B30" t="n">
         <v>57383</v>
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>509403</v>
+        <v>509380</v>
       </c>
       <c r="R30" t="n">
-        <v>7107783</v>
+        <v>7107864</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 55030-2024 artfynd.xlsx
+++ b/artfynd/A 55030-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122507149</v>
+        <v>122507167</v>
       </c>
       <c r="B2" t="n">
         <v>57383</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509392</v>
+        <v>509416</v>
       </c>
       <c r="R2" t="n">
-        <v>7107885</v>
+        <v>7107735</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122507152</v>
+        <v>122507173</v>
       </c>
       <c r="B3" t="n">
-        <v>57383</v>
+        <v>90857</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509408</v>
+        <v>509355</v>
       </c>
       <c r="R3" t="n">
-        <v>7107858</v>
+        <v>7107795</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122507136</v>
+        <v>122507169</v>
       </c>
       <c r="B4" t="n">
-        <v>57383</v>
+        <v>57536</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,34 +900,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Myrsnipmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509333</v>
+        <v>509389</v>
       </c>
       <c r="R4" t="n">
-        <v>7107799</v>
+        <v>7107816</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +964,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +990,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122507167</v>
+        <v>122507137</v>
       </c>
       <c r="B5" t="n">
         <v>57383</v>
@@ -1036,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509416</v>
+        <v>509318</v>
       </c>
       <c r="R5" t="n">
-        <v>7107735</v>
+        <v>7107804</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1070,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1097,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122507158</v>
+        <v>122507144</v>
       </c>
       <c r="B6" t="n">
         <v>57383</v>
@@ -1143,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509396</v>
+        <v>509334</v>
       </c>
       <c r="R6" t="n">
-        <v>7107815</v>
+        <v>7107923</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1177,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1204,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122507144</v>
+        <v>122507134</v>
       </c>
       <c r="B7" t="n">
         <v>57383</v>
@@ -1250,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>509334</v>
+        <v>509339</v>
       </c>
       <c r="R7" t="n">
-        <v>7107923</v>
+        <v>7107807</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122507170</v>
+        <v>122507142</v>
       </c>
       <c r="B8" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>509393</v>
+        <v>509307</v>
       </c>
       <c r="R8" t="n">
-        <v>7107823</v>
+        <v>7107977</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,6 +1387,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,7 +1418,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122507142</v>
+        <v>122507146</v>
       </c>
       <c r="B9" t="n">
         <v>57383</v>
@@ -1459,10 +1458,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509307</v>
+        <v>509321</v>
       </c>
       <c r="R9" t="n">
-        <v>7107977</v>
+        <v>7107910</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1498,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,7 +1525,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122507148</v>
+        <v>122507161</v>
       </c>
       <c r="B10" t="n">
         <v>57383</v>
@@ -1566,10 +1565,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509350</v>
+        <v>509403</v>
       </c>
       <c r="R10" t="n">
-        <v>7107857</v>
+        <v>7107783</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,7 +1605,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1633,10 +1632,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122507138</v>
+        <v>122507175</v>
       </c>
       <c r="B11" t="n">
-        <v>57383</v>
+        <v>90857</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,21 +1648,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509236</v>
+        <v>509283</v>
       </c>
       <c r="R11" t="n">
-        <v>7107905</v>
+        <v>7107892</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,11 +1708,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1740,7 +1734,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122507159</v>
+        <v>122507163</v>
       </c>
       <c r="B12" t="n">
         <v>57383</v>
@@ -1780,10 +1774,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>509402</v>
+        <v>509410</v>
       </c>
       <c r="R12" t="n">
-        <v>7107791</v>
+        <v>7107764</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1847,7 +1841,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122507141</v>
+        <v>122507165</v>
       </c>
       <c r="B13" t="n">
         <v>57383</v>
@@ -1887,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>509290</v>
+        <v>509420</v>
       </c>
       <c r="R13" t="n">
-        <v>7107974</v>
+        <v>7107746</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2061,10 +2055,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122507169</v>
+        <v>122507135</v>
       </c>
       <c r="B15" t="n">
-        <v>57536</v>
+        <v>57383</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2077,38 +2071,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Myrsnipmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>509389</v>
+        <v>509339</v>
       </c>
       <c r="R15" t="n">
-        <v>7107816</v>
+        <v>7107799</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,6 +2131,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2167,10 +2162,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122507143</v>
+        <v>122507170</v>
       </c>
       <c r="B16" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2183,21 +2178,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2207,10 +2202,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>509335</v>
+        <v>509393</v>
       </c>
       <c r="R16" t="n">
-        <v>7107936</v>
+        <v>7107823</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,11 +2238,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2274,7 +2264,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122507140</v>
+        <v>122507152</v>
       </c>
       <c r="B17" t="n">
         <v>57383</v>
@@ -2314,10 +2304,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>509279</v>
+        <v>509408</v>
       </c>
       <c r="R17" t="n">
-        <v>7107952</v>
+        <v>7107858</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2381,7 +2371,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122507165</v>
+        <v>122507149</v>
       </c>
       <c r="B18" t="n">
         <v>57383</v>
@@ -2421,10 +2411,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>509420</v>
+        <v>509392</v>
       </c>
       <c r="R18" t="n">
-        <v>7107746</v>
+        <v>7107885</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2488,7 +2478,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122507155</v>
+        <v>122507143</v>
       </c>
       <c r="B19" t="n">
         <v>57383</v>
@@ -2528,10 +2518,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>509385</v>
+        <v>509335</v>
       </c>
       <c r="R19" t="n">
-        <v>7107815</v>
+        <v>7107936</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2568,7 +2558,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2595,7 +2585,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122507146</v>
+        <v>122507147</v>
       </c>
       <c r="B20" t="n">
         <v>57383</v>
@@ -2635,10 +2625,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>509321</v>
+        <v>509307</v>
       </c>
       <c r="R20" t="n">
-        <v>7107910</v>
+        <v>7107890</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2675,7 +2665,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2702,7 +2692,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122507150</v>
+        <v>122507148</v>
       </c>
       <c r="B21" t="n">
         <v>57383</v>
@@ -2742,10 +2732,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>509389</v>
+        <v>509350</v>
       </c>
       <c r="R21" t="n">
-        <v>7107890</v>
+        <v>7107857</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2809,7 +2799,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122507134</v>
+        <v>122507159</v>
       </c>
       <c r="B22" t="n">
         <v>57383</v>
@@ -2849,10 +2839,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>509339</v>
+        <v>509402</v>
       </c>
       <c r="R22" t="n">
-        <v>7107807</v>
+        <v>7107791</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2916,7 +2906,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122507135</v>
+        <v>122507145</v>
       </c>
       <c r="B23" t="n">
         <v>57383</v>
@@ -2956,10 +2946,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>509339</v>
+        <v>509335</v>
       </c>
       <c r="R23" t="n">
-        <v>7107799</v>
+        <v>7107908</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2996,7 +2986,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3023,10 +3013,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122507175</v>
+        <v>122507153</v>
       </c>
       <c r="B24" t="n">
-        <v>90857</v>
+        <v>57383</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3039,21 +3029,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3063,10 +3053,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>509283</v>
+        <v>509398</v>
       </c>
       <c r="R24" t="n">
-        <v>7107892</v>
+        <v>7107862</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3099,6 +3089,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3125,7 +3120,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122507145</v>
+        <v>122507136</v>
       </c>
       <c r="B25" t="n">
         <v>57383</v>
@@ -3165,10 +3160,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>509335</v>
+        <v>509333</v>
       </c>
       <c r="R25" t="n">
-        <v>7107908</v>
+        <v>7107799</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3232,7 +3227,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122507147</v>
+        <v>122507138</v>
       </c>
       <c r="B26" t="n">
         <v>57383</v>
@@ -3272,10 +3267,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>509307</v>
+        <v>509236</v>
       </c>
       <c r="R26" t="n">
-        <v>7107890</v>
+        <v>7107905</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3339,7 +3334,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122507163</v>
+        <v>122507140</v>
       </c>
       <c r="B27" t="n">
         <v>57383</v>
@@ -3379,10 +3374,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>509410</v>
+        <v>509279</v>
       </c>
       <c r="R27" t="n">
-        <v>7107764</v>
+        <v>7107952</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3419,7 +3414,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3446,10 +3441,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122507173</v>
+        <v>122507155</v>
       </c>
       <c r="B28" t="n">
-        <v>90857</v>
+        <v>57383</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3462,21 +3457,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3486,10 +3481,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>509355</v>
+        <v>509385</v>
       </c>
       <c r="R28" t="n">
-        <v>7107795</v>
+        <v>7107815</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3522,6 +3517,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3548,7 +3548,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122507161</v>
+        <v>122507154</v>
       </c>
       <c r="B29" t="n">
         <v>57383</v>
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>509403</v>
+        <v>509380</v>
       </c>
       <c r="R29" t="n">
-        <v>7107783</v>
+        <v>7107864</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3655,7 +3655,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122507154</v>
+        <v>122507158</v>
       </c>
       <c r="B30" t="n">
         <v>57383</v>
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>509380</v>
+        <v>509396</v>
       </c>
       <c r="R30" t="n">
-        <v>7107864</v>
+        <v>7107815</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3762,7 +3762,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122507137</v>
+        <v>122507150</v>
       </c>
       <c r="B31" t="n">
         <v>57383</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>509318</v>
+        <v>509389</v>
       </c>
       <c r="R31" t="n">
-        <v>7107804</v>
+        <v>7107890</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3869,7 +3869,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122507153</v>
+        <v>122507141</v>
       </c>
       <c r="B32" t="n">
         <v>57383</v>
@@ -3909,10 +3909,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>509398</v>
+        <v>509290</v>
       </c>
       <c r="R32" t="n">
-        <v>7107862</v>
+        <v>7107974</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3949,7 +3949,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 55030-2024 artfynd.xlsx
+++ b/artfynd/A 55030-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122507167</v>
+        <v>122507163</v>
       </c>
       <c r="B2" t="n">
         <v>57383</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509416</v>
+        <v>509410</v>
       </c>
       <c r="R2" t="n">
-        <v>7107735</v>
+        <v>7107764</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122507173</v>
+        <v>122507152</v>
       </c>
       <c r="B3" t="n">
-        <v>90857</v>
+        <v>57383</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509355</v>
+        <v>509408</v>
       </c>
       <c r="R3" t="n">
-        <v>7107795</v>
+        <v>7107858</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122507169</v>
+        <v>122507138</v>
       </c>
       <c r="B4" t="n">
-        <v>57536</v>
+        <v>57383</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,38 +905,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Myrsnipmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509389</v>
+        <v>509236</v>
       </c>
       <c r="R4" t="n">
-        <v>7107816</v>
+        <v>7107905</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1097,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122507144</v>
+        <v>122507147</v>
       </c>
       <c r="B6" t="n">
         <v>57383</v>
@@ -1137,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509334</v>
+        <v>509307</v>
       </c>
       <c r="R6" t="n">
-        <v>7107923</v>
+        <v>7107890</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1177,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1204,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122507134</v>
+        <v>122507145</v>
       </c>
       <c r="B7" t="n">
         <v>57383</v>
@@ -1244,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>509339</v>
+        <v>509335</v>
       </c>
       <c r="R7" t="n">
-        <v>7107807</v>
+        <v>7107908</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122507142</v>
+        <v>122507153</v>
       </c>
       <c r="B8" t="n">
         <v>57383</v>
@@ -1351,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>509307</v>
+        <v>509398</v>
       </c>
       <c r="R8" t="n">
-        <v>7107977</v>
+        <v>7107862</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1391,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1418,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122507146</v>
+        <v>122507165</v>
       </c>
       <c r="B9" t="n">
         <v>57383</v>
@@ -1458,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509321</v>
+        <v>509420</v>
       </c>
       <c r="R9" t="n">
-        <v>7107910</v>
+        <v>7107746</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1498,7 +1504,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1525,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122507161</v>
+        <v>122507167</v>
       </c>
       <c r="B10" t="n">
         <v>57383</v>
@@ -1565,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509403</v>
+        <v>509416</v>
       </c>
       <c r="R10" t="n">
-        <v>7107783</v>
+        <v>7107735</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1605,7 +1611,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1632,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122507175</v>
+        <v>122507149</v>
       </c>
       <c r="B11" t="n">
-        <v>90857</v>
+        <v>57383</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1648,21 +1654,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1672,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509283</v>
+        <v>509392</v>
       </c>
       <c r="R11" t="n">
-        <v>7107892</v>
+        <v>7107885</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,6 +1714,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1734,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122507163</v>
+        <v>122507161</v>
       </c>
       <c r="B12" t="n">
         <v>57383</v>
@@ -1774,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>509410</v>
+        <v>509403</v>
       </c>
       <c r="R12" t="n">
-        <v>7107764</v>
+        <v>7107783</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,7 +1852,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122507165</v>
+        <v>122507144</v>
       </c>
       <c r="B13" t="n">
         <v>57383</v>
@@ -1881,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>509420</v>
+        <v>509334</v>
       </c>
       <c r="R13" t="n">
-        <v>7107746</v>
+        <v>7107923</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122507151</v>
+        <v>122507175</v>
       </c>
       <c r="B14" t="n">
-        <v>57383</v>
+        <v>90851</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1964,21 +1975,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1988,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>509412</v>
+        <v>509283</v>
       </c>
       <c r="R14" t="n">
-        <v>7107874</v>
+        <v>7107892</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2024,11 +2035,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2055,7 +2061,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122507135</v>
+        <v>122507142</v>
       </c>
       <c r="B15" t="n">
         <v>57383</v>
@@ -2095,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>509339</v>
+        <v>509307</v>
       </c>
       <c r="R15" t="n">
-        <v>7107799</v>
+        <v>7107977</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2135,7 +2141,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2162,10 +2168,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122507170</v>
+        <v>122507154</v>
       </c>
       <c r="B16" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2178,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2202,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>509393</v>
+        <v>509380</v>
       </c>
       <c r="R16" t="n">
-        <v>7107823</v>
+        <v>7107864</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2238,6 +2244,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2264,7 +2275,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122507152</v>
+        <v>122507141</v>
       </c>
       <c r="B17" t="n">
         <v>57383</v>
@@ -2304,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>509408</v>
+        <v>509290</v>
       </c>
       <c r="R17" t="n">
-        <v>7107858</v>
+        <v>7107974</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2344,7 +2355,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2371,7 +2382,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122507149</v>
+        <v>122507150</v>
       </c>
       <c r="B18" t="n">
         <v>57383</v>
@@ -2411,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>509392</v>
+        <v>509389</v>
       </c>
       <c r="R18" t="n">
-        <v>7107885</v>
+        <v>7107890</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2451,7 +2462,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2478,7 +2489,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122507143</v>
+        <v>122507148</v>
       </c>
       <c r="B19" t="n">
         <v>57383</v>
@@ -2518,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>509335</v>
+        <v>509350</v>
       </c>
       <c r="R19" t="n">
-        <v>7107936</v>
+        <v>7107857</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2558,7 +2569,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2585,7 +2596,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122507147</v>
+        <v>122507151</v>
       </c>
       <c r="B20" t="n">
         <v>57383</v>
@@ -2625,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>509307</v>
+        <v>509412</v>
       </c>
       <c r="R20" t="n">
-        <v>7107890</v>
+        <v>7107874</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2665,7 +2676,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2692,7 +2703,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122507148</v>
+        <v>122507155</v>
       </c>
       <c r="B21" t="n">
         <v>57383</v>
@@ -2732,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>509350</v>
+        <v>509385</v>
       </c>
       <c r="R21" t="n">
-        <v>7107857</v>
+        <v>7107815</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2799,7 +2810,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122507159</v>
+        <v>122507143</v>
       </c>
       <c r="B22" t="n">
         <v>57383</v>
@@ -2839,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>509402</v>
+        <v>509335</v>
       </c>
       <c r="R22" t="n">
-        <v>7107791</v>
+        <v>7107936</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2906,7 +2917,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122507145</v>
+        <v>122507146</v>
       </c>
       <c r="B23" t="n">
         <v>57383</v>
@@ -2946,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>509335</v>
+        <v>509321</v>
       </c>
       <c r="R23" t="n">
-        <v>7107908</v>
+        <v>7107910</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2986,7 +2997,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3013,10 +3024,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122507153</v>
+        <v>122507173</v>
       </c>
       <c r="B24" t="n">
-        <v>57383</v>
+        <v>90851</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3029,21 +3040,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3053,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>509398</v>
+        <v>509355</v>
       </c>
       <c r="R24" t="n">
-        <v>7107862</v>
+        <v>7107795</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3089,11 +3100,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3120,7 +3126,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122507136</v>
+        <v>122507134</v>
       </c>
       <c r="B25" t="n">
         <v>57383</v>
@@ -3160,10 +3166,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>509333</v>
+        <v>509339</v>
       </c>
       <c r="R25" t="n">
-        <v>7107799</v>
+        <v>7107807</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3227,7 +3233,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122507138</v>
+        <v>122507136</v>
       </c>
       <c r="B26" t="n">
         <v>57383</v>
@@ -3267,10 +3273,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>509236</v>
+        <v>509333</v>
       </c>
       <c r="R26" t="n">
-        <v>7107905</v>
+        <v>7107799</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3307,7 +3313,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3441,7 +3447,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122507155</v>
+        <v>122507158</v>
       </c>
       <c r="B28" t="n">
         <v>57383</v>
@@ -3481,7 +3487,7 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>509385</v>
+        <v>509396</v>
       </c>
       <c r="R28" t="n">
         <v>7107815</v>
@@ -3521,7 +3527,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3548,10 +3554,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122507154</v>
+        <v>122507170</v>
       </c>
       <c r="B29" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3564,21 +3570,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3588,10 +3594,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>509380</v>
+        <v>509393</v>
       </c>
       <c r="R29" t="n">
-        <v>7107864</v>
+        <v>7107823</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3624,11 +3630,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3655,7 +3656,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122507158</v>
+        <v>122507159</v>
       </c>
       <c r="B30" t="n">
         <v>57383</v>
@@ -3695,10 +3696,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>509396</v>
+        <v>509402</v>
       </c>
       <c r="R30" t="n">
-        <v>7107815</v>
+        <v>7107791</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3735,7 +3736,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3762,7 +3763,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122507150</v>
+        <v>122507135</v>
       </c>
       <c r="B31" t="n">
         <v>57383</v>
@@ -3802,10 +3803,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>509389</v>
+        <v>509339</v>
       </c>
       <c r="R31" t="n">
-        <v>7107890</v>
+        <v>7107799</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3869,10 +3870,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122507141</v>
+        <v>122507169</v>
       </c>
       <c r="B32" t="n">
-        <v>57383</v>
+        <v>57536</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3885,34 +3886,38 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Myrsnipmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>509290</v>
+        <v>509389</v>
       </c>
       <c r="R32" t="n">
-        <v>7107974</v>
+        <v>7107816</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3945,11 +3950,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 55030-2024 artfynd.xlsx
+++ b/artfynd/A 55030-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122507163</v>
+        <v>122507150</v>
       </c>
       <c r="B2" t="n">
         <v>57383</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509410</v>
+        <v>509389</v>
       </c>
       <c r="R2" t="n">
-        <v>7107764</v>
+        <v>7107890</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122507152</v>
+        <v>122507147</v>
       </c>
       <c r="B3" t="n">
         <v>57383</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509408</v>
+        <v>509307</v>
       </c>
       <c r="R3" t="n">
-        <v>7107858</v>
+        <v>7107890</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122507138</v>
+        <v>122507152</v>
       </c>
       <c r="B4" t="n">
         <v>57383</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509236</v>
+        <v>509408</v>
       </c>
       <c r="R4" t="n">
-        <v>7107905</v>
+        <v>7107858</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122507137</v>
+        <v>122507158</v>
       </c>
       <c r="B5" t="n">
         <v>57383</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509318</v>
+        <v>509396</v>
       </c>
       <c r="R5" t="n">
-        <v>7107804</v>
+        <v>7107815</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122507147</v>
+        <v>122507165</v>
       </c>
       <c r="B6" t="n">
         <v>57383</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509307</v>
+        <v>509420</v>
       </c>
       <c r="R6" t="n">
-        <v>7107890</v>
+        <v>7107746</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122507145</v>
+        <v>122507153</v>
       </c>
       <c r="B7" t="n">
         <v>57383</v>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>509335</v>
+        <v>509398</v>
       </c>
       <c r="R7" t="n">
-        <v>7107908</v>
+        <v>7107862</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122507153</v>
+        <v>122507144</v>
       </c>
       <c r="B8" t="n">
         <v>57383</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>509398</v>
+        <v>509334</v>
       </c>
       <c r="R8" t="n">
-        <v>7107862</v>
+        <v>7107923</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,7 +1424,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122507165</v>
+        <v>122507167</v>
       </c>
       <c r="B9" t="n">
         <v>57383</v>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509420</v>
+        <v>509416</v>
       </c>
       <c r="R9" t="n">
-        <v>7107746</v>
+        <v>7107735</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122507167</v>
+        <v>122507138</v>
       </c>
       <c r="B10" t="n">
         <v>57383</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509416</v>
+        <v>509236</v>
       </c>
       <c r="R10" t="n">
-        <v>7107735</v>
+        <v>7107905</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122507149</v>
+        <v>122507163</v>
       </c>
       <c r="B11" t="n">
         <v>57383</v>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509392</v>
+        <v>509410</v>
       </c>
       <c r="R11" t="n">
-        <v>7107885</v>
+        <v>7107764</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122507161</v>
+        <v>122507148</v>
       </c>
       <c r="B12" t="n">
         <v>57383</v>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>509403</v>
+        <v>509350</v>
       </c>
       <c r="R12" t="n">
-        <v>7107783</v>
+        <v>7107857</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,7 +1852,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122507144</v>
+        <v>122507141</v>
       </c>
       <c r="B13" t="n">
         <v>57383</v>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>509334</v>
+        <v>509290</v>
       </c>
       <c r="R13" t="n">
-        <v>7107923</v>
+        <v>7107974</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122507175</v>
+        <v>122507136</v>
       </c>
       <c r="B14" t="n">
-        <v>90851</v>
+        <v>57383</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1975,21 +1975,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>509283</v>
+        <v>509333</v>
       </c>
       <c r="R14" t="n">
-        <v>7107892</v>
+        <v>7107799</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2035,6 +2035,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2061,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122507142</v>
+        <v>122507173</v>
       </c>
       <c r="B15" t="n">
-        <v>57383</v>
+        <v>90851</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2077,21 +2082,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>509307</v>
+        <v>509355</v>
       </c>
       <c r="R15" t="n">
-        <v>7107977</v>
+        <v>7107795</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2137,11 +2142,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2168,10 +2168,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122507154</v>
+        <v>122507169</v>
       </c>
       <c r="B16" t="n">
-        <v>57383</v>
+        <v>57536</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2184,34 +2184,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Myrsnipmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>509380</v>
+        <v>509389</v>
       </c>
       <c r="R16" t="n">
-        <v>7107864</v>
+        <v>7107816</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2244,11 +2248,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2275,7 +2274,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122507141</v>
+        <v>122507135</v>
       </c>
       <c r="B17" t="n">
         <v>57383</v>
@@ -2315,10 +2314,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>509290</v>
+        <v>509339</v>
       </c>
       <c r="R17" t="n">
-        <v>7107974</v>
+        <v>7107799</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2355,7 +2354,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2382,10 +2381,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122507150</v>
+        <v>122507170</v>
       </c>
       <c r="B18" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2398,21 +2397,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2421,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>509389</v>
+        <v>509393</v>
       </c>
       <c r="R18" t="n">
-        <v>7107890</v>
+        <v>7107823</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2458,11 +2457,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2489,7 +2483,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122507148</v>
+        <v>122507151</v>
       </c>
       <c r="B19" t="n">
         <v>57383</v>
@@ -2529,10 +2523,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>509350</v>
+        <v>509412</v>
       </c>
       <c r="R19" t="n">
-        <v>7107857</v>
+        <v>7107874</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2596,7 +2590,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122507151</v>
+        <v>122507155</v>
       </c>
       <c r="B20" t="n">
         <v>57383</v>
@@ -2636,10 +2630,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>509412</v>
+        <v>509385</v>
       </c>
       <c r="R20" t="n">
-        <v>7107874</v>
+        <v>7107815</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2703,7 +2697,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122507155</v>
+        <v>122507134</v>
       </c>
       <c r="B21" t="n">
         <v>57383</v>
@@ -2743,10 +2737,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>509385</v>
+        <v>509339</v>
       </c>
       <c r="R21" t="n">
-        <v>7107815</v>
+        <v>7107807</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2783,7 +2777,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2810,10 +2804,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122507143</v>
+        <v>122507175</v>
       </c>
       <c r="B22" t="n">
-        <v>57383</v>
+        <v>90851</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2826,21 +2820,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2850,10 +2844,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>509335</v>
+        <v>509283</v>
       </c>
       <c r="R22" t="n">
-        <v>7107936</v>
+        <v>7107892</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2886,11 +2880,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3024,10 +3013,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122507173</v>
+        <v>122507159</v>
       </c>
       <c r="B24" t="n">
-        <v>90851</v>
+        <v>57383</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3040,21 +3029,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3064,10 +3053,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>509355</v>
+        <v>509402</v>
       </c>
       <c r="R24" t="n">
-        <v>7107795</v>
+        <v>7107791</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3100,6 +3089,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3126,7 +3120,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122507134</v>
+        <v>122507149</v>
       </c>
       <c r="B25" t="n">
         <v>57383</v>
@@ -3166,10 +3160,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>509339</v>
+        <v>509392</v>
       </c>
       <c r="R25" t="n">
-        <v>7107807</v>
+        <v>7107885</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3233,7 +3227,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122507136</v>
+        <v>122507142</v>
       </c>
       <c r="B26" t="n">
         <v>57383</v>
@@ -3273,10 +3267,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>509333</v>
+        <v>509307</v>
       </c>
       <c r="R26" t="n">
-        <v>7107799</v>
+        <v>7107977</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3340,7 +3334,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122507140</v>
+        <v>122507161</v>
       </c>
       <c r="B27" t="n">
         <v>57383</v>
@@ -3380,10 +3374,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>509279</v>
+        <v>509403</v>
       </c>
       <c r="R27" t="n">
-        <v>7107952</v>
+        <v>7107783</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,7 +3414,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3447,7 +3441,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122507158</v>
+        <v>122507154</v>
       </c>
       <c r="B28" t="n">
         <v>57383</v>
@@ -3487,10 +3481,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>509396</v>
+        <v>509380</v>
       </c>
       <c r="R28" t="n">
-        <v>7107815</v>
+        <v>7107864</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3527,7 +3521,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3554,10 +3548,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122507170</v>
+        <v>122507137</v>
       </c>
       <c r="B29" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3570,21 +3564,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3594,10 +3588,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>509393</v>
+        <v>509318</v>
       </c>
       <c r="R29" t="n">
-        <v>7107823</v>
+        <v>7107804</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3630,6 +3624,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3656,7 +3655,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122507159</v>
+        <v>122507140</v>
       </c>
       <c r="B30" t="n">
         <v>57383</v>
@@ -3696,10 +3695,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>509402</v>
+        <v>509279</v>
       </c>
       <c r="R30" t="n">
-        <v>7107791</v>
+        <v>7107952</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3736,7 +3735,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3763,7 +3762,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122507135</v>
+        <v>122507143</v>
       </c>
       <c r="B31" t="n">
         <v>57383</v>
@@ -3803,10 +3802,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>509339</v>
+        <v>509335</v>
       </c>
       <c r="R31" t="n">
-        <v>7107799</v>
+        <v>7107936</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3843,7 +3842,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3870,10 +3869,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122507169</v>
+        <v>122507145</v>
       </c>
       <c r="B32" t="n">
-        <v>57536</v>
+        <v>57383</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3886,38 +3885,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Myrsnipmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>509389</v>
+        <v>509335</v>
       </c>
       <c r="R32" t="n">
-        <v>7107816</v>
+        <v>7107908</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3950,6 +3945,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 55030-2024 artfynd.xlsx
+++ b/artfynd/A 55030-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122507150</v>
+        <v>122507146</v>
       </c>
       <c r="B2" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509389</v>
+        <v>509321</v>
       </c>
       <c r="R2" t="n">
-        <v>7107890</v>
+        <v>7107910</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122507147</v>
+        <v>122507137</v>
       </c>
       <c r="B3" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509307</v>
+        <v>509318</v>
       </c>
       <c r="R3" t="n">
-        <v>7107890</v>
+        <v>7107804</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122507152</v>
+        <v>122507151</v>
       </c>
       <c r="B4" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509408</v>
+        <v>509412</v>
       </c>
       <c r="R4" t="n">
-        <v>7107858</v>
+        <v>7107874</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122507158</v>
+        <v>122507159</v>
       </c>
       <c r="B5" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509396</v>
+        <v>509402</v>
       </c>
       <c r="R5" t="n">
-        <v>7107815</v>
+        <v>7107791</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122507165</v>
+        <v>122507145</v>
       </c>
       <c r="B6" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509420</v>
+        <v>509335</v>
       </c>
       <c r="R6" t="n">
-        <v>7107746</v>
+        <v>7107908</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122507153</v>
+        <v>122507143</v>
       </c>
       <c r="B7" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>509398</v>
+        <v>509335</v>
       </c>
       <c r="R7" t="n">
-        <v>7107862</v>
+        <v>7107936</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122507144</v>
+        <v>122507149</v>
       </c>
       <c r="B8" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>509334</v>
+        <v>509392</v>
       </c>
       <c r="R8" t="n">
-        <v>7107923</v>
+        <v>7107885</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122507167</v>
+        <v>122507150</v>
       </c>
       <c r="B9" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509416</v>
+        <v>509389</v>
       </c>
       <c r="R9" t="n">
-        <v>7107735</v>
+        <v>7107890</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122507138</v>
+        <v>122507153</v>
       </c>
       <c r="B10" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509236</v>
+        <v>509398</v>
       </c>
       <c r="R10" t="n">
-        <v>7107905</v>
+        <v>7107862</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122507163</v>
+        <v>122507167</v>
       </c>
       <c r="B11" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509410</v>
+        <v>509416</v>
       </c>
       <c r="R11" t="n">
-        <v>7107764</v>
+        <v>7107735</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122507148</v>
+        <v>122507135</v>
       </c>
       <c r="B12" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>509350</v>
+        <v>509339</v>
       </c>
       <c r="R12" t="n">
-        <v>7107857</v>
+        <v>7107799</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122507141</v>
+        <v>122507161</v>
       </c>
       <c r="B13" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>509290</v>
+        <v>509403</v>
       </c>
       <c r="R13" t="n">
-        <v>7107974</v>
+        <v>7107783</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122507136</v>
+        <v>122507154</v>
       </c>
       <c r="B14" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>509333</v>
+        <v>509380</v>
       </c>
       <c r="R14" t="n">
-        <v>7107799</v>
+        <v>7107864</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2066,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122507173</v>
+        <v>122507155</v>
       </c>
       <c r="B15" t="n">
-        <v>90851</v>
+        <v>57384</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2082,21 +2082,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>509355</v>
+        <v>509385</v>
       </c>
       <c r="R15" t="n">
-        <v>7107795</v>
+        <v>7107815</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2142,6 +2142,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2168,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122507169</v>
+        <v>122507138</v>
       </c>
       <c r="B16" t="n">
-        <v>57536</v>
+        <v>57384</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2184,38 +2189,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Myrsnipmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>509389</v>
+        <v>509236</v>
       </c>
       <c r="R16" t="n">
-        <v>7107816</v>
+        <v>7107905</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2248,6 +2249,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2274,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122507135</v>
+        <v>122507142</v>
       </c>
       <c r="B17" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2314,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>509339</v>
+        <v>509307</v>
       </c>
       <c r="R17" t="n">
-        <v>7107799</v>
+        <v>7107977</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2354,7 +2360,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2381,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122507170</v>
+        <v>122507140</v>
       </c>
       <c r="B18" t="n">
-        <v>79737</v>
+        <v>57384</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2397,21 +2403,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2421,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>509393</v>
+        <v>509279</v>
       </c>
       <c r="R18" t="n">
-        <v>7107823</v>
+        <v>7107952</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,6 +2463,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2483,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122507151</v>
+        <v>122507175</v>
       </c>
       <c r="B19" t="n">
-        <v>57383</v>
+        <v>90852</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2499,21 +2510,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2523,10 +2534,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>509412</v>
+        <v>509283</v>
       </c>
       <c r="R19" t="n">
-        <v>7107874</v>
+        <v>7107892</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2559,11 +2570,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2590,10 +2596,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122507155</v>
+        <v>122507144</v>
       </c>
       <c r="B20" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2630,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>509385</v>
+        <v>509334</v>
       </c>
       <c r="R20" t="n">
-        <v>7107815</v>
+        <v>7107923</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2670,7 +2676,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2697,10 +2703,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122507134</v>
+        <v>122507173</v>
       </c>
       <c r="B21" t="n">
-        <v>57383</v>
+        <v>90852</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2713,21 +2719,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2737,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>509339</v>
+        <v>509355</v>
       </c>
       <c r="R21" t="n">
-        <v>7107807</v>
+        <v>7107795</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2773,11 +2779,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2804,10 +2805,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122507175</v>
+        <v>122507170</v>
       </c>
       <c r="B22" t="n">
-        <v>90851</v>
+        <v>79738</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2820,21 +2821,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2844,10 +2845,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>509283</v>
+        <v>509393</v>
       </c>
       <c r="R22" t="n">
-        <v>7107892</v>
+        <v>7107823</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2906,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122507146</v>
+        <v>122507169</v>
       </c>
       <c r="B23" t="n">
-        <v>57383</v>
+        <v>57537</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2922,34 +2923,38 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Myrsnipmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>509321</v>
+        <v>509389</v>
       </c>
       <c r="R23" t="n">
-        <v>7107910</v>
+        <v>7107816</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2982,11 +2987,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3013,10 +3013,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122507159</v>
+        <v>122507163</v>
       </c>
       <c r="B24" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>509402</v>
+        <v>509410</v>
       </c>
       <c r="R24" t="n">
-        <v>7107791</v>
+        <v>7107764</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3120,10 +3120,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122507149</v>
+        <v>122507134</v>
       </c>
       <c r="B25" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3160,10 +3160,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>509392</v>
+        <v>509339</v>
       </c>
       <c r="R25" t="n">
-        <v>7107885</v>
+        <v>7107807</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3227,10 +3227,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122507142</v>
+        <v>122507152</v>
       </c>
       <c r="B26" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3267,10 +3267,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>509307</v>
+        <v>509408</v>
       </c>
       <c r="R26" t="n">
-        <v>7107977</v>
+        <v>7107858</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3334,10 +3334,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122507161</v>
+        <v>122507148</v>
       </c>
       <c r="B27" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3374,10 +3374,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>509403</v>
+        <v>509350</v>
       </c>
       <c r="R27" t="n">
-        <v>7107783</v>
+        <v>7107857</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3441,10 +3441,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122507154</v>
+        <v>122507141</v>
       </c>
       <c r="B28" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3481,10 +3481,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>509380</v>
+        <v>509290</v>
       </c>
       <c r="R28" t="n">
-        <v>7107864</v>
+        <v>7107974</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3548,10 +3548,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122507137</v>
+        <v>122507147</v>
       </c>
       <c r="B29" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>509318</v>
+        <v>509307</v>
       </c>
       <c r="R29" t="n">
-        <v>7107804</v>
+        <v>7107890</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3655,10 +3655,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122507140</v>
+        <v>122507136</v>
       </c>
       <c r="B30" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>509279</v>
+        <v>509333</v>
       </c>
       <c r="R30" t="n">
-        <v>7107952</v>
+        <v>7107799</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3762,10 +3762,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122507143</v>
+        <v>122507158</v>
       </c>
       <c r="B31" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>509335</v>
+        <v>509396</v>
       </c>
       <c r="R31" t="n">
-        <v>7107936</v>
+        <v>7107815</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3869,10 +3869,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122507145</v>
+        <v>122507165</v>
       </c>
       <c r="B32" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3909,10 +3909,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>509335</v>
+        <v>509420</v>
       </c>
       <c r="R32" t="n">
-        <v>7107908</v>
+        <v>7107746</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 55030-2024 artfynd.xlsx
+++ b/artfynd/A 55030-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122507146</v>
+        <v>122507136</v>
       </c>
       <c r="B2" t="n">
         <v>57384</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509321</v>
+        <v>509333</v>
       </c>
       <c r="R2" t="n">
-        <v>7107910</v>
+        <v>7107799</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122507137</v>
+        <v>122507169</v>
       </c>
       <c r="B3" t="n">
-        <v>57384</v>
+        <v>57537</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,34 +798,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Myrsnipmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509318</v>
+        <v>509389</v>
       </c>
       <c r="R3" t="n">
-        <v>7107804</v>
+        <v>7107816</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +862,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122507151</v>
+        <v>122507173</v>
       </c>
       <c r="B4" t="n">
-        <v>57384</v>
+        <v>90855</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509412</v>
+        <v>509355</v>
       </c>
       <c r="R4" t="n">
-        <v>7107874</v>
+        <v>7107795</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +964,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +990,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122507159</v>
+        <v>122507142</v>
       </c>
       <c r="B5" t="n">
         <v>57384</v>
@@ -1036,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509402</v>
+        <v>509307</v>
       </c>
       <c r="R5" t="n">
-        <v>7107791</v>
+        <v>7107977</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1097,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122507145</v>
+        <v>122507163</v>
       </c>
       <c r="B6" t="n">
         <v>57384</v>
@@ -1143,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509335</v>
+        <v>509410</v>
       </c>
       <c r="R6" t="n">
-        <v>7107908</v>
+        <v>7107764</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,7 +1204,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122507143</v>
+        <v>122507152</v>
       </c>
       <c r="B7" t="n">
         <v>57384</v>
@@ -1250,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>509335</v>
+        <v>509408</v>
       </c>
       <c r="R7" t="n">
-        <v>7107936</v>
+        <v>7107858</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1284,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1311,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122507149</v>
+        <v>122507150</v>
       </c>
       <c r="B8" t="n">
         <v>57384</v>
@@ -1357,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>509392</v>
+        <v>509389</v>
       </c>
       <c r="R8" t="n">
-        <v>7107885</v>
+        <v>7107890</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1391,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,7 +1418,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122507150</v>
+        <v>122507158</v>
       </c>
       <c r="B9" t="n">
         <v>57384</v>
@@ -1464,10 +1458,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509389</v>
+        <v>509396</v>
       </c>
       <c r="R9" t="n">
-        <v>7107890</v>
+        <v>7107815</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1498,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,7 +1525,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122507153</v>
+        <v>122507141</v>
       </c>
       <c r="B10" t="n">
         <v>57384</v>
@@ -1571,10 +1565,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509398</v>
+        <v>509290</v>
       </c>
       <c r="R10" t="n">
-        <v>7107862</v>
+        <v>7107974</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1605,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,7 +1632,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122507167</v>
+        <v>122507140</v>
       </c>
       <c r="B11" t="n">
         <v>57384</v>
@@ -1678,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509416</v>
+        <v>509279</v>
       </c>
       <c r="R11" t="n">
-        <v>7107735</v>
+        <v>7107952</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,7 +1739,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122507135</v>
+        <v>122507148</v>
       </c>
       <c r="B12" t="n">
         <v>57384</v>
@@ -1785,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>509339</v>
+        <v>509350</v>
       </c>
       <c r="R12" t="n">
-        <v>7107799</v>
+        <v>7107857</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1852,7 +1846,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122507161</v>
+        <v>122507153</v>
       </c>
       <c r="B13" t="n">
         <v>57384</v>
@@ -1892,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>509403</v>
+        <v>509398</v>
       </c>
       <c r="R13" t="n">
-        <v>7107783</v>
+        <v>7107862</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1926,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,7 +1953,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122507154</v>
+        <v>122507147</v>
       </c>
       <c r="B14" t="n">
         <v>57384</v>
@@ -1999,10 +1993,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>509380</v>
+        <v>509307</v>
       </c>
       <c r="R14" t="n">
-        <v>7107864</v>
+        <v>7107890</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2039,7 +2033,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,7 +2060,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122507155</v>
+        <v>122507167</v>
       </c>
       <c r="B15" t="n">
         <v>57384</v>
@@ -2106,10 +2100,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>509385</v>
+        <v>509416</v>
       </c>
       <c r="R15" t="n">
-        <v>7107815</v>
+        <v>7107735</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2173,7 +2167,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122507138</v>
+        <v>122507143</v>
       </c>
       <c r="B16" t="n">
         <v>57384</v>
@@ -2213,10 +2207,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>509236</v>
+        <v>509335</v>
       </c>
       <c r="R16" t="n">
-        <v>7107905</v>
+        <v>7107936</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2253,7 +2247,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,7 +2274,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122507142</v>
+        <v>122507165</v>
       </c>
       <c r="B17" t="n">
         <v>57384</v>
@@ -2320,10 +2314,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>509307</v>
+        <v>509420</v>
       </c>
       <c r="R17" t="n">
-        <v>7107977</v>
+        <v>7107746</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2387,7 +2381,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122507140</v>
+        <v>122507134</v>
       </c>
       <c r="B18" t="n">
         <v>57384</v>
@@ -2427,10 +2421,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>509279</v>
+        <v>509339</v>
       </c>
       <c r="R18" t="n">
-        <v>7107952</v>
+        <v>7107807</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2467,7 +2461,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2497,7 +2491,7 @@
         <v>122507175</v>
       </c>
       <c r="B19" t="n">
-        <v>90852</v>
+        <v>90855</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2596,7 +2590,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122507144</v>
+        <v>122507137</v>
       </c>
       <c r="B20" t="n">
         <v>57384</v>
@@ -2636,10 +2630,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>509334</v>
+        <v>509318</v>
       </c>
       <c r="R20" t="n">
-        <v>7107923</v>
+        <v>7107804</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2676,7 +2670,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2703,10 +2697,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122507173</v>
+        <v>122507154</v>
       </c>
       <c r="B21" t="n">
-        <v>90852</v>
+        <v>57384</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2719,21 +2713,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2743,10 +2737,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>509355</v>
+        <v>509380</v>
       </c>
       <c r="R21" t="n">
-        <v>7107795</v>
+        <v>7107864</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2779,6 +2773,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2805,10 +2804,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122507170</v>
+        <v>122507135</v>
       </c>
       <c r="B22" t="n">
-        <v>79738</v>
+        <v>57384</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2821,21 +2820,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2845,10 +2844,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>509393</v>
+        <v>509339</v>
       </c>
       <c r="R22" t="n">
-        <v>7107823</v>
+        <v>7107799</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2881,6 +2880,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2907,10 +2911,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122507169</v>
+        <v>122507155</v>
       </c>
       <c r="B23" t="n">
-        <v>57537</v>
+        <v>57384</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2923,38 +2927,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Myrsnipmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>509389</v>
+        <v>509385</v>
       </c>
       <c r="R23" t="n">
-        <v>7107816</v>
+        <v>7107815</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2987,6 +2987,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3013,7 +3018,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122507163</v>
+        <v>122507149</v>
       </c>
       <c r="B24" t="n">
         <v>57384</v>
@@ -3053,10 +3058,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>509410</v>
+        <v>509392</v>
       </c>
       <c r="R24" t="n">
-        <v>7107764</v>
+        <v>7107885</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3120,7 +3125,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122507134</v>
+        <v>122507159</v>
       </c>
       <c r="B25" t="n">
         <v>57384</v>
@@ -3160,10 +3165,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>509339</v>
+        <v>509402</v>
       </c>
       <c r="R25" t="n">
-        <v>7107807</v>
+        <v>7107791</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3227,7 +3232,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122507152</v>
+        <v>122507145</v>
       </c>
       <c r="B26" t="n">
         <v>57384</v>
@@ -3267,10 +3272,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>509408</v>
+        <v>509335</v>
       </c>
       <c r="R26" t="n">
-        <v>7107858</v>
+        <v>7107908</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3307,7 +3312,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3334,10 +3339,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122507148</v>
+        <v>122507170</v>
       </c>
       <c r="B27" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3350,21 +3355,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3374,10 +3379,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>509350</v>
+        <v>509393</v>
       </c>
       <c r="R27" t="n">
-        <v>7107857</v>
+        <v>7107823</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3410,11 +3415,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3441,7 +3441,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122507141</v>
+        <v>122507144</v>
       </c>
       <c r="B28" t="n">
         <v>57384</v>
@@ -3481,10 +3481,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>509290</v>
+        <v>509334</v>
       </c>
       <c r="R28" t="n">
-        <v>7107974</v>
+        <v>7107923</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3548,7 +3548,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122507147</v>
+        <v>122507138</v>
       </c>
       <c r="B29" t="n">
         <v>57384</v>
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>509307</v>
+        <v>509236</v>
       </c>
       <c r="R29" t="n">
-        <v>7107890</v>
+        <v>7107905</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3655,7 +3655,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122507136</v>
+        <v>122507146</v>
       </c>
       <c r="B30" t="n">
         <v>57384</v>
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>509333</v>
+        <v>509321</v>
       </c>
       <c r="R30" t="n">
-        <v>7107799</v>
+        <v>7107910</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3762,7 +3762,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122507158</v>
+        <v>122507151</v>
       </c>
       <c r="B31" t="n">
         <v>57384</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>509396</v>
+        <v>509412</v>
       </c>
       <c r="R31" t="n">
-        <v>7107815</v>
+        <v>7107874</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3869,7 +3869,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122507165</v>
+        <v>122507161</v>
       </c>
       <c r="B32" t="n">
         <v>57384</v>
@@ -3909,10 +3909,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>509420</v>
+        <v>509403</v>
       </c>
       <c r="R32" t="n">
-        <v>7107746</v>
+        <v>7107783</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 55030-2024 artfynd.xlsx
+++ b/artfynd/A 55030-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122507136</v>
+        <v>122507137</v>
       </c>
       <c r="B2" t="n">
         <v>57384</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509333</v>
+        <v>509318</v>
       </c>
       <c r="R2" t="n">
-        <v>7107799</v>
+        <v>7107804</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122507169</v>
+        <v>122507143</v>
       </c>
       <c r="B3" t="n">
-        <v>57537</v>
+        <v>57384</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,38 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Myrsnipmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509389</v>
+        <v>509335</v>
       </c>
       <c r="R3" t="n">
-        <v>7107816</v>
+        <v>7107936</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122507173</v>
+        <v>122507148</v>
       </c>
       <c r="B4" t="n">
-        <v>90855</v>
+        <v>57384</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509355</v>
+        <v>509350</v>
       </c>
       <c r="R4" t="n">
-        <v>7107795</v>
+        <v>7107857</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -990,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122507142</v>
+        <v>122507151</v>
       </c>
       <c r="B5" t="n">
         <v>57384</v>
@@ -1030,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509307</v>
+        <v>509412</v>
       </c>
       <c r="R5" t="n">
-        <v>7107977</v>
+        <v>7107874</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1070,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122507163</v>
+        <v>122507135</v>
       </c>
       <c r="B6" t="n">
         <v>57384</v>
@@ -1137,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509410</v>
+        <v>509339</v>
       </c>
       <c r="R6" t="n">
-        <v>7107764</v>
+        <v>7107799</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1177,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1204,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122507152</v>
+        <v>122507173</v>
       </c>
       <c r="B7" t="n">
-        <v>57384</v>
+        <v>90855</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1220,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1244,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>509408</v>
+        <v>509355</v>
       </c>
       <c r="R7" t="n">
-        <v>7107858</v>
+        <v>7107795</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,11 +1286,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1311,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122507150</v>
+        <v>122507170</v>
       </c>
       <c r="B8" t="n">
-        <v>57384</v>
+        <v>79741</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>509389</v>
+        <v>509393</v>
       </c>
       <c r="R8" t="n">
-        <v>7107890</v>
+        <v>7107823</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,11 +1388,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1418,7 +1414,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122507158</v>
+        <v>122507147</v>
       </c>
       <c r="B9" t="n">
         <v>57384</v>
@@ -1458,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509396</v>
+        <v>509307</v>
       </c>
       <c r="R9" t="n">
-        <v>7107815</v>
+        <v>7107890</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,7 +1521,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122507141</v>
+        <v>122507140</v>
       </c>
       <c r="B10" t="n">
         <v>57384</v>
@@ -1565,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509290</v>
+        <v>509279</v>
       </c>
       <c r="R10" t="n">
-        <v>7107974</v>
+        <v>7107952</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1605,7 +1601,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1632,7 +1628,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122507140</v>
+        <v>122507138</v>
       </c>
       <c r="B11" t="n">
         <v>57384</v>
@@ -1672,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509279</v>
+        <v>509236</v>
       </c>
       <c r="R11" t="n">
-        <v>7107952</v>
+        <v>7107905</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1712,7 +1708,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1739,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122507148</v>
+        <v>122507175</v>
       </c>
       <c r="B12" t="n">
-        <v>57384</v>
+        <v>90855</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1755,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1779,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>509350</v>
+        <v>509283</v>
       </c>
       <c r="R12" t="n">
-        <v>7107857</v>
+        <v>7107892</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,11 +1811,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1846,7 +1837,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122507153</v>
+        <v>122507167</v>
       </c>
       <c r="B13" t="n">
         <v>57384</v>
@@ -1886,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>509398</v>
+        <v>509416</v>
       </c>
       <c r="R13" t="n">
-        <v>7107862</v>
+        <v>7107735</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1953,7 +1944,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122507147</v>
+        <v>122507155</v>
       </c>
       <c r="B14" t="n">
         <v>57384</v>
@@ -1993,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>509307</v>
+        <v>509385</v>
       </c>
       <c r="R14" t="n">
-        <v>7107890</v>
+        <v>7107815</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2033,7 +2024,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2060,7 +2051,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122507167</v>
+        <v>122507159</v>
       </c>
       <c r="B15" t="n">
         <v>57384</v>
@@ -2100,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>509416</v>
+        <v>509402</v>
       </c>
       <c r="R15" t="n">
-        <v>7107735</v>
+        <v>7107791</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2140,7 +2131,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2167,7 +2158,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122507143</v>
+        <v>122507142</v>
       </c>
       <c r="B16" t="n">
         <v>57384</v>
@@ -2207,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>509335</v>
+        <v>509307</v>
       </c>
       <c r="R16" t="n">
-        <v>7107936</v>
+        <v>7107977</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2274,7 +2265,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122507165</v>
+        <v>122507152</v>
       </c>
       <c r="B17" t="n">
         <v>57384</v>
@@ -2314,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>509420</v>
+        <v>509408</v>
       </c>
       <c r="R17" t="n">
-        <v>7107746</v>
+        <v>7107858</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2354,7 +2345,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2381,7 +2372,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122507134</v>
+        <v>122507150</v>
       </c>
       <c r="B18" t="n">
         <v>57384</v>
@@ -2421,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>509339</v>
+        <v>509389</v>
       </c>
       <c r="R18" t="n">
-        <v>7107807</v>
+        <v>7107890</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2461,7 +2452,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2488,10 +2479,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122507175</v>
+        <v>122507161</v>
       </c>
       <c r="B19" t="n">
-        <v>90855</v>
+        <v>57384</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2504,21 +2495,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2528,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>509283</v>
+        <v>509403</v>
       </c>
       <c r="R19" t="n">
-        <v>7107892</v>
+        <v>7107783</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,6 +2555,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2590,7 +2586,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122507137</v>
+        <v>122507146</v>
       </c>
       <c r="B20" t="n">
         <v>57384</v>
@@ -2630,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>509318</v>
+        <v>509321</v>
       </c>
       <c r="R20" t="n">
-        <v>7107804</v>
+        <v>7107910</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2670,7 +2666,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2697,7 +2693,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122507154</v>
+        <v>122507165</v>
       </c>
       <c r="B21" t="n">
         <v>57384</v>
@@ -2737,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>509380</v>
+        <v>509420</v>
       </c>
       <c r="R21" t="n">
-        <v>7107864</v>
+        <v>7107746</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2804,7 +2800,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122507135</v>
+        <v>122507149</v>
       </c>
       <c r="B22" t="n">
         <v>57384</v>
@@ -2844,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>509339</v>
+        <v>509392</v>
       </c>
       <c r="R22" t="n">
-        <v>7107799</v>
+        <v>7107885</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2884,7 +2880,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2911,7 +2907,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122507155</v>
+        <v>122507154</v>
       </c>
       <c r="B23" t="n">
         <v>57384</v>
@@ -2951,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>509385</v>
+        <v>509380</v>
       </c>
       <c r="R23" t="n">
-        <v>7107815</v>
+        <v>7107864</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2991,7 +2987,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3018,7 +3014,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122507149</v>
+        <v>122507141</v>
       </c>
       <c r="B24" t="n">
         <v>57384</v>
@@ -3058,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>509392</v>
+        <v>509290</v>
       </c>
       <c r="R24" t="n">
-        <v>7107885</v>
+        <v>7107974</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3125,7 +3121,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122507159</v>
+        <v>122507163</v>
       </c>
       <c r="B25" t="n">
         <v>57384</v>
@@ -3165,10 +3161,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>509402</v>
+        <v>509410</v>
       </c>
       <c r="R25" t="n">
-        <v>7107791</v>
+        <v>7107764</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3232,7 +3228,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122507145</v>
+        <v>122507144</v>
       </c>
       <c r="B26" t="n">
         <v>57384</v>
@@ -3272,10 +3268,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>509335</v>
+        <v>509334</v>
       </c>
       <c r="R26" t="n">
-        <v>7107908</v>
+        <v>7107923</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3339,10 +3335,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122507170</v>
+        <v>122507169</v>
       </c>
       <c r="B27" t="n">
-        <v>79741</v>
+        <v>57537</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3355,34 +3351,38 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Myrsnipmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>509393</v>
+        <v>509389</v>
       </c>
       <c r="R27" t="n">
-        <v>7107823</v>
+        <v>7107816</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3441,7 +3441,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122507144</v>
+        <v>122507158</v>
       </c>
       <c r="B28" t="n">
         <v>57384</v>
@@ -3481,10 +3481,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>509334</v>
+        <v>509396</v>
       </c>
       <c r="R28" t="n">
-        <v>7107923</v>
+        <v>7107815</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3548,7 +3548,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122507138</v>
+        <v>122507153</v>
       </c>
       <c r="B29" t="n">
         <v>57384</v>
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>509236</v>
+        <v>509398</v>
       </c>
       <c r="R29" t="n">
-        <v>7107905</v>
+        <v>7107862</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3655,7 +3655,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122507146</v>
+        <v>122507134</v>
       </c>
       <c r="B30" t="n">
         <v>57384</v>
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>509321</v>
+        <v>509339</v>
       </c>
       <c r="R30" t="n">
-        <v>7107910</v>
+        <v>7107807</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3762,7 +3762,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122507151</v>
+        <v>122507145</v>
       </c>
       <c r="B31" t="n">
         <v>57384</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>509412</v>
+        <v>509335</v>
       </c>
       <c r="R31" t="n">
-        <v>7107874</v>
+        <v>7107908</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3869,7 +3869,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122507161</v>
+        <v>122507136</v>
       </c>
       <c r="B32" t="n">
         <v>57384</v>
@@ -3909,10 +3909,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>509403</v>
+        <v>509333</v>
       </c>
       <c r="R32" t="n">
-        <v>7107783</v>
+        <v>7107799</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 55030-2024 artfynd.xlsx
+++ b/artfynd/A 55030-2024 artfynd.xlsx
@@ -3344,10 +3344,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122507170</v>
+        <v>122507161</v>
       </c>
       <c r="B27" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3360,21 +3360,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3384,10 +3384,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>509393</v>
+        <v>509403</v>
       </c>
       <c r="R27" t="n">
-        <v>7107823</v>
+        <v>7107783</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,6 +3420,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3446,10 +3451,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122507161</v>
+        <v>122507170</v>
       </c>
       <c r="B28" t="n">
-        <v>57478</v>
+        <v>79843</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3462,21 +3467,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3486,10 +3491,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>509403</v>
+        <v>509393</v>
       </c>
       <c r="R28" t="n">
-        <v>7107783</v>
+        <v>7107823</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3522,11 +3527,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 55030-2024 artfynd.xlsx
+++ b/artfynd/A 55030-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122507152</v>
+        <v>122507158</v>
       </c>
       <c r="B2" t="n">
         <v>57478</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509408</v>
+        <v>509396</v>
       </c>
       <c r="R2" t="n">
-        <v>7107858</v>
+        <v>7107815</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122507153</v>
+        <v>122507163</v>
       </c>
       <c r="B3" t="n">
         <v>57478</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509398</v>
+        <v>509410</v>
       </c>
       <c r="R3" t="n">
-        <v>7107862</v>
+        <v>7107764</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122507151</v>
+        <v>122507142</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509412</v>
+        <v>509307</v>
       </c>
       <c r="R4" t="n">
-        <v>7107874</v>
+        <v>7107977</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122507169</v>
+        <v>122507175</v>
       </c>
       <c r="B5" t="n">
-        <v>57631</v>
+        <v>90962</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,38 +1012,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Myrsnipmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509389</v>
+        <v>509283</v>
       </c>
       <c r="R5" t="n">
-        <v>7107816</v>
+        <v>7107892</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122507149</v>
+        <v>122507134</v>
       </c>
       <c r="B6" t="n">
         <v>57478</v>
@@ -1142,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509392</v>
+        <v>509339</v>
       </c>
       <c r="R6" t="n">
-        <v>7107885</v>
+        <v>7107807</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122507167</v>
+        <v>122507145</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1249,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>509416</v>
+        <v>509335</v>
       </c>
       <c r="R7" t="n">
-        <v>7107735</v>
+        <v>7107908</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1289,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122507138</v>
+        <v>122507150</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1356,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>509236</v>
+        <v>509389</v>
       </c>
       <c r="R8" t="n">
-        <v>7107905</v>
+        <v>7107890</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1396,7 +1392,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1423,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122507145</v>
+        <v>122507140</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1463,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509335</v>
+        <v>509279</v>
       </c>
       <c r="R9" t="n">
-        <v>7107908</v>
+        <v>7107952</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1503,7 +1499,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1530,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122507159</v>
+        <v>122507173</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1546,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1570,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509402</v>
+        <v>509355</v>
       </c>
       <c r="R10" t="n">
-        <v>7107791</v>
+        <v>7107795</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,11 +1602,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1637,7 +1628,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122507137</v>
+        <v>122507146</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1677,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509318</v>
+        <v>509321</v>
       </c>
       <c r="R11" t="n">
-        <v>7107804</v>
+        <v>7107910</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1717,7 +1708,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1744,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122507144</v>
+        <v>122507136</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1784,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>509334</v>
+        <v>509333</v>
       </c>
       <c r="R12" t="n">
-        <v>7107923</v>
+        <v>7107799</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1851,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122507148</v>
+        <v>122507147</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -1891,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>509350</v>
+        <v>509307</v>
       </c>
       <c r="R13" t="n">
-        <v>7107857</v>
+        <v>7107890</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1931,7 +1922,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1958,7 +1949,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122507136</v>
+        <v>122507144</v>
       </c>
       <c r="B14" t="n">
         <v>57478</v>
@@ -1998,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>509333</v>
+        <v>509334</v>
       </c>
       <c r="R14" t="n">
-        <v>7107799</v>
+        <v>7107923</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2065,7 +2056,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122507134</v>
+        <v>122507165</v>
       </c>
       <c r="B15" t="n">
         <v>57478</v>
@@ -2105,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>509339</v>
+        <v>509420</v>
       </c>
       <c r="R15" t="n">
-        <v>7107807</v>
+        <v>7107746</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2172,7 +2163,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122507135</v>
+        <v>122507149</v>
       </c>
       <c r="B16" t="n">
         <v>57478</v>
@@ -2212,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>509339</v>
+        <v>509392</v>
       </c>
       <c r="R16" t="n">
-        <v>7107799</v>
+        <v>7107885</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2252,7 +2243,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2279,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122507142</v>
+        <v>122507170</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2295,21 +2286,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2319,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>509307</v>
+        <v>509393</v>
       </c>
       <c r="R17" t="n">
-        <v>7107977</v>
+        <v>7107823</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2355,11 +2346,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2386,10 +2372,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122507175</v>
+        <v>122507155</v>
       </c>
       <c r="B18" t="n">
-        <v>90958</v>
+        <v>57478</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2402,21 +2388,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2426,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>509283</v>
+        <v>509385</v>
       </c>
       <c r="R18" t="n">
-        <v>7107892</v>
+        <v>7107815</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2462,6 +2448,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2488,7 +2479,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122507147</v>
+        <v>122507143</v>
       </c>
       <c r="B19" t="n">
         <v>57478</v>
@@ -2528,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>509307</v>
+        <v>509335</v>
       </c>
       <c r="R19" t="n">
-        <v>7107890</v>
+        <v>7107936</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2568,7 +2559,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2595,7 +2586,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122507150</v>
+        <v>122507167</v>
       </c>
       <c r="B20" t="n">
         <v>57478</v>
@@ -2635,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>509389</v>
+        <v>509416</v>
       </c>
       <c r="R20" t="n">
-        <v>7107890</v>
+        <v>7107735</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2702,7 +2693,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122507140</v>
+        <v>122507151</v>
       </c>
       <c r="B21" t="n">
         <v>57478</v>
@@ -2742,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>509279</v>
+        <v>509412</v>
       </c>
       <c r="R21" t="n">
-        <v>7107952</v>
+        <v>7107874</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2809,7 +2800,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122507165</v>
+        <v>122507159</v>
       </c>
       <c r="B22" t="n">
         <v>57478</v>
@@ -2849,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>509420</v>
+        <v>509402</v>
       </c>
       <c r="R22" t="n">
-        <v>7107746</v>
+        <v>7107791</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2916,7 +2907,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122507155</v>
+        <v>122507137</v>
       </c>
       <c r="B23" t="n">
         <v>57478</v>
@@ -2956,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>509385</v>
+        <v>509318</v>
       </c>
       <c r="R23" t="n">
-        <v>7107815</v>
+        <v>7107804</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2996,7 +2987,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3023,7 +3014,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122507163</v>
+        <v>122507141</v>
       </c>
       <c r="B24" t="n">
         <v>57478</v>
@@ -3063,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>509410</v>
+        <v>509290</v>
       </c>
       <c r="R24" t="n">
-        <v>7107764</v>
+        <v>7107974</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3130,7 +3121,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122507158</v>
+        <v>122507154</v>
       </c>
       <c r="B25" t="n">
         <v>57478</v>
@@ -3170,10 +3161,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>509396</v>
+        <v>509380</v>
       </c>
       <c r="R25" t="n">
-        <v>7107815</v>
+        <v>7107864</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3210,7 +3201,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3237,7 +3228,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122507141</v>
+        <v>122507153</v>
       </c>
       <c r="B26" t="n">
         <v>57478</v>
@@ -3277,10 +3268,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>509290</v>
+        <v>509398</v>
       </c>
       <c r="R26" t="n">
-        <v>7107974</v>
+        <v>7107862</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3317,7 +3308,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3344,10 +3335,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122507161</v>
+        <v>122507169</v>
       </c>
       <c r="B27" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3360,34 +3351,38 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Myrsnipmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>509403</v>
+        <v>509389</v>
       </c>
       <c r="R27" t="n">
-        <v>7107783</v>
+        <v>7107816</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,11 +3415,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3451,10 +3441,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122507170</v>
+        <v>122507152</v>
       </c>
       <c r="B28" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3467,21 +3457,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3491,10 +3481,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>509393</v>
+        <v>509408</v>
       </c>
       <c r="R28" t="n">
-        <v>7107823</v>
+        <v>7107858</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3527,6 +3517,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3553,7 +3548,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122507143</v>
+        <v>122507135</v>
       </c>
       <c r="B29" t="n">
         <v>57478</v>
@@ -3593,10 +3588,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>509335</v>
+        <v>509339</v>
       </c>
       <c r="R29" t="n">
-        <v>7107936</v>
+        <v>7107799</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3633,7 +3628,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3660,7 +3655,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122507154</v>
+        <v>122507148</v>
       </c>
       <c r="B30" t="n">
         <v>57478</v>
@@ -3700,10 +3695,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>509380</v>
+        <v>509350</v>
       </c>
       <c r="R30" t="n">
-        <v>7107864</v>
+        <v>7107857</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3740,7 +3735,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3767,10 +3762,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122507173</v>
+        <v>122507161</v>
       </c>
       <c r="B31" t="n">
-        <v>90958</v>
+        <v>57478</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3783,21 +3778,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3807,10 +3802,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>509355</v>
+        <v>509403</v>
       </c>
       <c r="R31" t="n">
-        <v>7107795</v>
+        <v>7107783</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3843,6 +3838,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3869,7 +3869,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122507146</v>
+        <v>122507138</v>
       </c>
       <c r="B32" t="n">
         <v>57478</v>
@@ -3909,10 +3909,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>509321</v>
+        <v>509236</v>
       </c>
       <c r="R32" t="n">
-        <v>7107910</v>
+        <v>7107905</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3949,7 +3949,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 55030-2024 artfynd.xlsx
+++ b/artfynd/A 55030-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122507158</v>
+        <v>122507137</v>
       </c>
       <c r="B2" t="n">
         <v>57478</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509396</v>
+        <v>509318</v>
       </c>
       <c r="R2" t="n">
-        <v>7107815</v>
+        <v>7107804</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122507163</v>
+        <v>122507159</v>
       </c>
       <c r="B3" t="n">
         <v>57478</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509410</v>
+        <v>509402</v>
       </c>
       <c r="R3" t="n">
-        <v>7107764</v>
+        <v>7107791</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122507142</v>
+        <v>122507143</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509307</v>
+        <v>509335</v>
       </c>
       <c r="R4" t="n">
-        <v>7107977</v>
+        <v>7107936</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122507175</v>
+        <v>122507173</v>
       </c>
       <c r="B5" t="n">
         <v>90962</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509283</v>
+        <v>509355</v>
       </c>
       <c r="R5" t="n">
-        <v>7107892</v>
+        <v>7107795</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122507134</v>
+        <v>122507154</v>
       </c>
       <c r="B6" t="n">
         <v>57478</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509339</v>
+        <v>509380</v>
       </c>
       <c r="R6" t="n">
-        <v>7107807</v>
+        <v>7107864</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122507145</v>
+        <v>122507151</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>509335</v>
+        <v>509412</v>
       </c>
       <c r="R7" t="n">
-        <v>7107908</v>
+        <v>7107874</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122507150</v>
+        <v>122507152</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>509389</v>
+        <v>509408</v>
       </c>
       <c r="R8" t="n">
-        <v>7107890</v>
+        <v>7107858</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,7 +1419,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122507140</v>
+        <v>122507165</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509279</v>
+        <v>509420</v>
       </c>
       <c r="R9" t="n">
-        <v>7107952</v>
+        <v>7107746</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122507173</v>
+        <v>122507169</v>
       </c>
       <c r="B10" t="n">
-        <v>90962</v>
+        <v>57631</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,34 +1542,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Myrsnipmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509355</v>
+        <v>509389</v>
       </c>
       <c r="R10" t="n">
-        <v>7107795</v>
+        <v>7107816</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1628,7 +1632,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122507146</v>
+        <v>122507144</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1668,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509321</v>
+        <v>509334</v>
       </c>
       <c r="R11" t="n">
-        <v>7107910</v>
+        <v>7107923</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1712,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,7 +1739,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122507136</v>
+        <v>122507146</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1775,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>509333</v>
+        <v>509321</v>
       </c>
       <c r="R12" t="n">
-        <v>7107799</v>
+        <v>7107910</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1819,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1949,7 +1953,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122507144</v>
+        <v>122507155</v>
       </c>
       <c r="B14" t="n">
         <v>57478</v>
@@ -1989,10 +1993,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>509334</v>
+        <v>509385</v>
       </c>
       <c r="R14" t="n">
-        <v>7107923</v>
+        <v>7107815</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2033,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,10 +2060,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122507165</v>
+        <v>122507175</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2072,21 +2076,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2096,10 +2100,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>509420</v>
+        <v>509283</v>
       </c>
       <c r="R15" t="n">
-        <v>7107746</v>
+        <v>7107892</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2132,11 +2136,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2163,7 +2162,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122507149</v>
+        <v>122507163</v>
       </c>
       <c r="B16" t="n">
         <v>57478</v>
@@ -2203,10 +2202,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>509392</v>
+        <v>509410</v>
       </c>
       <c r="R16" t="n">
-        <v>7107885</v>
+        <v>7107764</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2270,10 +2269,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122507170</v>
+        <v>122507136</v>
       </c>
       <c r="B17" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2286,21 +2285,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2310,10 +2309,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>509393</v>
+        <v>509333</v>
       </c>
       <c r="R17" t="n">
-        <v>7107823</v>
+        <v>7107799</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2346,6 +2345,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2372,7 +2376,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122507155</v>
+        <v>122507161</v>
       </c>
       <c r="B18" t="n">
         <v>57478</v>
@@ -2412,10 +2416,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>509385</v>
+        <v>509403</v>
       </c>
       <c r="R18" t="n">
-        <v>7107815</v>
+        <v>7107783</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2452,7 +2456,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2479,7 +2483,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122507143</v>
+        <v>122507145</v>
       </c>
       <c r="B19" t="n">
         <v>57478</v>
@@ -2522,7 +2526,7 @@
         <v>509335</v>
       </c>
       <c r="R19" t="n">
-        <v>7107936</v>
+        <v>7107908</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2586,7 +2590,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122507167</v>
+        <v>122507149</v>
       </c>
       <c r="B20" t="n">
         <v>57478</v>
@@ -2626,10 +2630,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>509416</v>
+        <v>509392</v>
       </c>
       <c r="R20" t="n">
-        <v>7107735</v>
+        <v>7107885</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2666,7 +2670,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2693,7 +2697,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122507151</v>
+        <v>122507148</v>
       </c>
       <c r="B21" t="n">
         <v>57478</v>
@@ -2733,10 +2737,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>509412</v>
+        <v>509350</v>
       </c>
       <c r="R21" t="n">
-        <v>7107874</v>
+        <v>7107857</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2800,7 +2804,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122507159</v>
+        <v>122507153</v>
       </c>
       <c r="B22" t="n">
         <v>57478</v>
@@ -2840,10 +2844,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>509402</v>
+        <v>509398</v>
       </c>
       <c r="R22" t="n">
-        <v>7107791</v>
+        <v>7107862</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2880,7 +2884,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2907,7 +2911,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122507137</v>
+        <v>122507134</v>
       </c>
       <c r="B23" t="n">
         <v>57478</v>
@@ -2947,10 +2951,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>509318</v>
+        <v>509339</v>
       </c>
       <c r="R23" t="n">
-        <v>7107804</v>
+        <v>7107807</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2987,7 +2991,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3014,7 +3018,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122507141</v>
+        <v>122507140</v>
       </c>
       <c r="B24" t="n">
         <v>57478</v>
@@ -3054,10 +3058,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>509290</v>
+        <v>509279</v>
       </c>
       <c r="R24" t="n">
-        <v>7107974</v>
+        <v>7107952</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3094,7 +3098,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3121,7 +3125,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122507154</v>
+        <v>122507150</v>
       </c>
       <c r="B25" t="n">
         <v>57478</v>
@@ -3161,10 +3165,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>509380</v>
+        <v>509389</v>
       </c>
       <c r="R25" t="n">
-        <v>7107864</v>
+        <v>7107890</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3201,7 +3205,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3228,7 +3232,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122507153</v>
+        <v>122507167</v>
       </c>
       <c r="B26" t="n">
         <v>57478</v>
@@ -3268,10 +3272,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>509398</v>
+        <v>509416</v>
       </c>
       <c r="R26" t="n">
-        <v>7107862</v>
+        <v>7107735</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3335,10 +3339,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122507169</v>
+        <v>122507170</v>
       </c>
       <c r="B27" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3351,38 +3355,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Myrsnipmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>509389</v>
+        <v>509393</v>
       </c>
       <c r="R27" t="n">
-        <v>7107816</v>
+        <v>7107823</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3441,7 +3441,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122507152</v>
+        <v>122507158</v>
       </c>
       <c r="B28" t="n">
         <v>57478</v>
@@ -3481,10 +3481,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>509408</v>
+        <v>509396</v>
       </c>
       <c r="R28" t="n">
-        <v>7107858</v>
+        <v>7107815</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3548,7 +3548,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122507135</v>
+        <v>122507142</v>
       </c>
       <c r="B29" t="n">
         <v>57478</v>
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>509339</v>
+        <v>509307</v>
       </c>
       <c r="R29" t="n">
-        <v>7107799</v>
+        <v>7107977</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3655,7 +3655,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122507148</v>
+        <v>122507138</v>
       </c>
       <c r="B30" t="n">
         <v>57478</v>
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>509350</v>
+        <v>509236</v>
       </c>
       <c r="R30" t="n">
-        <v>7107857</v>
+        <v>7107905</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3762,7 +3762,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122507161</v>
+        <v>122507135</v>
       </c>
       <c r="B31" t="n">
         <v>57478</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>509403</v>
+        <v>509339</v>
       </c>
       <c r="R31" t="n">
-        <v>7107783</v>
+        <v>7107799</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3869,7 +3869,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122507138</v>
+        <v>122507141</v>
       </c>
       <c r="B32" t="n">
         <v>57478</v>
@@ -3909,10 +3909,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>509236</v>
+        <v>509290</v>
       </c>
       <c r="R32" t="n">
-        <v>7107905</v>
+        <v>7107974</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3949,7 +3949,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 55030-2024 artfynd.xlsx
+++ b/artfynd/A 55030-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122507137</v>
+        <v>122507152</v>
       </c>
       <c r="B2" t="n">
         <v>57478</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509318</v>
+        <v>509408</v>
       </c>
       <c r="R2" t="n">
-        <v>7107804</v>
+        <v>7107858</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122507159</v>
+        <v>122507170</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509402</v>
+        <v>509393</v>
       </c>
       <c r="R3" t="n">
-        <v>7107791</v>
+        <v>7107823</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122507143</v>
+        <v>122507150</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509335</v>
+        <v>509389</v>
       </c>
       <c r="R4" t="n">
-        <v>7107936</v>
+        <v>7107890</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122507173</v>
+        <v>122507155</v>
       </c>
       <c r="B5" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509355</v>
+        <v>509385</v>
       </c>
       <c r="R5" t="n">
-        <v>7107795</v>
+        <v>7107815</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,6 +1067,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122507154</v>
+        <v>122507159</v>
       </c>
       <c r="B6" t="n">
         <v>57478</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509380</v>
+        <v>509402</v>
       </c>
       <c r="R6" t="n">
-        <v>7107864</v>
+        <v>7107791</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122507151</v>
+        <v>122507163</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>509412</v>
+        <v>509410</v>
       </c>
       <c r="R7" t="n">
-        <v>7107874</v>
+        <v>7107764</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122507152</v>
+        <v>122507175</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>509408</v>
+        <v>509283</v>
       </c>
       <c r="R8" t="n">
-        <v>7107858</v>
+        <v>7107892</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,11 +1388,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,7 +1414,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122507165</v>
+        <v>122507146</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1459,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509420</v>
+        <v>509321</v>
       </c>
       <c r="R9" t="n">
-        <v>7107746</v>
+        <v>7107910</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1494,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122507169</v>
+        <v>122507154</v>
       </c>
       <c r="B10" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,38 +1537,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Myrsnipmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509389</v>
+        <v>509380</v>
       </c>
       <c r="R10" t="n">
-        <v>7107816</v>
+        <v>7107864</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,6 +1597,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1632,7 +1628,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122507144</v>
+        <v>122507137</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1672,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509334</v>
+        <v>509318</v>
       </c>
       <c r="R11" t="n">
-        <v>7107923</v>
+        <v>7107804</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1712,7 +1708,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1739,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122507146</v>
+        <v>122507167</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1779,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>509321</v>
+        <v>509416</v>
       </c>
       <c r="R12" t="n">
-        <v>7107910</v>
+        <v>7107735</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1846,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122507147</v>
+        <v>122507145</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -1886,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>509307</v>
+        <v>509335</v>
       </c>
       <c r="R13" t="n">
-        <v>7107890</v>
+        <v>7107908</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1926,7 +1922,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1953,7 +1949,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122507155</v>
+        <v>122507143</v>
       </c>
       <c r="B14" t="n">
         <v>57478</v>
@@ -1993,10 +1989,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>509385</v>
+        <v>509335</v>
       </c>
       <c r="R14" t="n">
-        <v>7107815</v>
+        <v>7107936</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2033,7 +2029,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2060,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122507175</v>
+        <v>122507142</v>
       </c>
       <c r="B15" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2076,21 +2072,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2100,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>509283</v>
+        <v>509307</v>
       </c>
       <c r="R15" t="n">
-        <v>7107892</v>
+        <v>7107977</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,6 +2132,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2162,7 +2163,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122507163</v>
+        <v>122507161</v>
       </c>
       <c r="B16" t="n">
         <v>57478</v>
@@ -2202,10 +2203,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>509410</v>
+        <v>509403</v>
       </c>
       <c r="R16" t="n">
-        <v>7107764</v>
+        <v>7107783</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2269,7 +2270,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122507136</v>
+        <v>122507151</v>
       </c>
       <c r="B17" t="n">
         <v>57478</v>
@@ -2309,10 +2310,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>509333</v>
+        <v>509412</v>
       </c>
       <c r="R17" t="n">
-        <v>7107799</v>
+        <v>7107874</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2349,7 +2350,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2376,7 +2377,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122507161</v>
+        <v>122507144</v>
       </c>
       <c r="B18" t="n">
         <v>57478</v>
@@ -2416,10 +2417,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>509403</v>
+        <v>509334</v>
       </c>
       <c r="R18" t="n">
-        <v>7107783</v>
+        <v>7107923</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2483,7 +2484,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122507145</v>
+        <v>122507140</v>
       </c>
       <c r="B19" t="n">
         <v>57478</v>
@@ -2523,10 +2524,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>509335</v>
+        <v>509279</v>
       </c>
       <c r="R19" t="n">
-        <v>7107908</v>
+        <v>7107952</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2563,7 +2564,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2590,10 +2591,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122507149</v>
+        <v>122507173</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2606,21 +2607,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2630,10 +2631,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>509392</v>
+        <v>509355</v>
       </c>
       <c r="R20" t="n">
-        <v>7107885</v>
+        <v>7107795</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2666,11 +2667,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2804,7 +2800,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122507153</v>
+        <v>122507165</v>
       </c>
       <c r="B22" t="n">
         <v>57478</v>
@@ -2844,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>509398</v>
+        <v>509420</v>
       </c>
       <c r="R22" t="n">
-        <v>7107862</v>
+        <v>7107746</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2884,7 +2880,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2911,7 +2907,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122507134</v>
+        <v>122507153</v>
       </c>
       <c r="B23" t="n">
         <v>57478</v>
@@ -2951,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>509339</v>
+        <v>509398</v>
       </c>
       <c r="R23" t="n">
-        <v>7107807</v>
+        <v>7107862</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2991,7 +2987,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3018,7 +3014,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122507140</v>
+        <v>122507158</v>
       </c>
       <c r="B24" t="n">
         <v>57478</v>
@@ -3058,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>509279</v>
+        <v>509396</v>
       </c>
       <c r="R24" t="n">
-        <v>7107952</v>
+        <v>7107815</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3098,7 +3094,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3125,7 +3121,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122507150</v>
+        <v>122507149</v>
       </c>
       <c r="B25" t="n">
         <v>57478</v>
@@ -3165,10 +3161,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>509389</v>
+        <v>509392</v>
       </c>
       <c r="R25" t="n">
-        <v>7107890</v>
+        <v>7107885</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3205,7 +3201,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3232,7 +3228,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122507167</v>
+        <v>122507138</v>
       </c>
       <c r="B26" t="n">
         <v>57478</v>
@@ -3272,10 +3268,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>509416</v>
+        <v>509236</v>
       </c>
       <c r="R26" t="n">
-        <v>7107735</v>
+        <v>7107905</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3312,7 +3308,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3339,10 +3335,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122507170</v>
+        <v>122507141</v>
       </c>
       <c r="B27" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3355,21 +3351,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3379,10 +3375,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>509393</v>
+        <v>509290</v>
       </c>
       <c r="R27" t="n">
-        <v>7107823</v>
+        <v>7107974</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3415,6 +3411,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3441,10 +3442,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122507158</v>
+        <v>122507169</v>
       </c>
       <c r="B28" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3457,34 +3458,38 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Myrsnipmyrarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>509396</v>
+        <v>509389</v>
       </c>
       <c r="R28" t="n">
-        <v>7107815</v>
+        <v>7107816</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3517,11 +3522,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3548,7 +3548,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122507142</v>
+        <v>122507136</v>
       </c>
       <c r="B29" t="n">
         <v>57478</v>
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>509307</v>
+        <v>509333</v>
       </c>
       <c r="R29" t="n">
-        <v>7107977</v>
+        <v>7107799</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3655,7 +3655,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122507138</v>
+        <v>122507147</v>
       </c>
       <c r="B30" t="n">
         <v>57478</v>
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>509236</v>
+        <v>509307</v>
       </c>
       <c r="R30" t="n">
-        <v>7107905</v>
+        <v>7107890</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3762,7 +3762,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122507135</v>
+        <v>122507134</v>
       </c>
       <c r="B31" t="n">
         <v>57478</v>
@@ -3805,7 +3805,7 @@
         <v>509339</v>
       </c>
       <c r="R31" t="n">
-        <v>7107799</v>
+        <v>7107807</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3869,7 +3869,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122507141</v>
+        <v>122507135</v>
       </c>
       <c r="B32" t="n">
         <v>57478</v>
@@ -3909,10 +3909,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>509290</v>
+        <v>509339</v>
       </c>
       <c r="R32" t="n">
-        <v>7107974</v>
+        <v>7107799</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3949,7 +3949,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 55030-2024 artfynd.xlsx
+++ b/artfynd/A 55030-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122507152</v>
+        <v>122507170</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509408</v>
+        <v>509393</v>
       </c>
       <c r="R2" t="n">
-        <v>7107858</v>
+        <v>7107823</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122507170</v>
+        <v>122507150</v>
       </c>
       <c r="B3" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>509393</v>
+        <v>509389</v>
       </c>
       <c r="R3" t="n">
-        <v>7107823</v>
+        <v>7107890</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122507150</v>
+        <v>122507155</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>509389</v>
+        <v>509385</v>
       </c>
       <c r="R4" t="n">
-        <v>7107890</v>
+        <v>7107815</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122507155</v>
+        <v>122507159</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509385</v>
+        <v>509402</v>
       </c>
       <c r="R5" t="n">
-        <v>7107815</v>
+        <v>7107791</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122507159</v>
+        <v>122507152</v>
       </c>
       <c r="B6" t="n">
         <v>57478</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509402</v>
+        <v>509408</v>
       </c>
       <c r="R6" t="n">
-        <v>7107791</v>
+        <v>7107858</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ringhack färska och äldre</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
